--- a/Job_Tracker.xlsx
+++ b/Job_Tracker.xlsx
@@ -439,7 +439,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -547,7 +547,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -1120,7 +1120,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -1798,7 +1798,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -2301,7 +2301,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2409,7 +2409,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -3381,7 +3381,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -3415,8 +3414,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3444,7 +3441,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -3478,8 +3474,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3507,7 +3501,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -3541,8 +3534,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3570,7 +3561,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -3604,8 +3594,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3619,7 +3607,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -3727,7 +3715,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -3834,8 +3822,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -4939,6 +4927,534 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SmartJobs_QLD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jobs_NT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Careers_VIC</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Monash_Health</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>23</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Western_Health</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>WA_Health</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Peninsula_Health</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>The_Womens</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Grampians_Health</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Eastern_Health</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>7</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>RANZCOG</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>RACP</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>JobRadars</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>403 Client Error: Forbidden for url: https://australia.jobradars.com/jobs?q=registrar+medical</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PageUp</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>pageup</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Mercy_Workday</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4951,7 +5467,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -6489,7 +7005,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -8399,7 +8915,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -8433,8 +8948,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10742,7 +11255,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -10776,8 +11288,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10805,7 +11315,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -10839,8 +11348,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10868,7 +11375,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -10902,8 +11408,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10931,7 +11435,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -10965,8 +11468,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17354,7 +17855,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -17462,7 +17963,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -18850,7 +19351,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -19372,7 +19873,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -19406,8 +19906,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19421,7 +19919,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -19529,7 +20027,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -19637,7 +20135,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -19745,7 +20243,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>

--- a/Job_Tracker.xlsx
+++ b/Job_Tracker.xlsx
@@ -1191,7 +1191,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -1225,8 +1224,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1239,7 +1236,6 @@
           <t>ICU</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>Grampians Health</t>
@@ -1255,7 +1251,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -1289,8 +1284,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1323,7 +1316,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -1357,8 +1349,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1371,7 +1361,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>Grampians Health</t>
@@ -1387,7 +1376,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -1421,8 +1409,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1455,7 +1441,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -1489,8 +1474,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1498,7 +1481,6 @@
           <t>International Job Seekers</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Intern</t>
@@ -1519,7 +1501,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -1553,8 +1534,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2301,7 +2280,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>Eastern Health</t>
@@ -2317,7 +2295,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -2351,8 +2328,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2360,7 +2335,6 @@
           <t>2027 Upper Gastro Intestinal Research Fellow</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Fellow</t>
@@ -2381,7 +2355,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -2415,8 +2388,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2585,11 +2556,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. Michael O'Brien</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -2769,7 +2740,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -2894,7 +2865,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -2954,7 +2925,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -4376,7 +4347,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -4410,7 +4380,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>High Match</t>
@@ -4448,7 +4417,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -4482,7 +4450,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>High Match</t>
@@ -4520,7 +4487,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -4554,7 +4520,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>High Match</t>
@@ -4592,7 +4557,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -4626,7 +4590,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>High Match</t>
@@ -4644,7 +4607,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -4660,7 +4622,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -4694,8 +4655,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4708,7 +4667,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -4724,7 +4682,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -4758,8 +4715,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4772,7 +4727,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -4788,7 +4742,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -4822,8 +4775,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4836,7 +4787,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -4852,7 +4802,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -4886,8 +4835,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4900,7 +4847,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -4916,7 +4862,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -4950,8 +4895,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4964,7 +4907,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -4980,7 +4922,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -5014,8 +4955,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5048,7 +4987,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -5082,8 +5020,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5116,7 +5052,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -5150,8 +5085,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5184,7 +5117,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -5218,8 +5150,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5252,7 +5182,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -5286,8 +5215,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5320,7 +5247,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -5354,8 +5280,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5388,7 +5312,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -5422,8 +5345,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5456,7 +5377,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -5490,8 +5410,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5504,7 +5422,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -5520,7 +5437,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -5554,8 +5470,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5563,7 +5477,6 @@
           <t>International Grants</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>Intern</t>
@@ -5584,7 +5497,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -5618,8 +5530,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5627,7 +5537,6 @@
           <t>Prizes, grants, scholarships and fellowships</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>Fellow</t>
@@ -5648,7 +5557,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -5682,8 +5590,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5924,7 +5830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7554,6 +7460,534 @@
       <c r="G49" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SmartJobs_QLD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>auto-disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Jobs_NT</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>auto-disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Careers_VIC</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>auto-disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Monash_Health</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>23</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Western_Health</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>12</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>WA_Health</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>auto-disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Peninsula_Health</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>auto-disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>The_Womens</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>auto-disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Grampians_Health</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>14</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Eastern_Health</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>12</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>7</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>RANZCOG</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>auto-disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>RACP</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>41</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>JobRadars</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>auto-disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>PageUp</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>pageup</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>auto-disabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>29-06-2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Mercy_Workday</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>auto-disabled</t>
         </is>
       </c>
     </row>
@@ -7666,12 +8100,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Grampians_Health</t>
+          <t>RCH</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Registrar - General Medicine Advanced Trainee</t>
+          <t>2027 Senior Registrar General Medicine</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7681,12 +8115,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Senior Registrar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Grampians Health</t>
+          <t>Royal Children's Hospital</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7701,11 +8135,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-General-Medicine-Advanced-Trainee-VIC-3350/1362283766/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Senior-Registrar-General-Medicine/1362878366/</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -7726,32 +8160,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Michael O'Brien</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Western_Health</t>
+          <t>Grampians_Health</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2027 Emergency Medicine Medical Officer</t>
+          <t>Registrar - General Medicine Advanced Trainee</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Emergency Medicine</t>
+          <t>General Medicine</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Medical Officer</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Western Health</t>
+          <t>Grampians Health</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7766,11 +8200,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://careers.wh.org.au/job/2027-Emergency-Medicine-Medical-Officer/1361118766/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-General-Medicine-Advanced-Trainee-VIC-3350/1362283766/</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -7791,7 +8225,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dr. Priya Sharma</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7801,17 +8235,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>General Practitioner - Custodial Health</t>
+          <t>2027 Emergency Medicine Medical Officer</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>General Practitioner (GP)</t>
+          <t>Emergency Medicine</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>General Practitioner (GP)</t>
+          <t>Medical Officer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -7831,11 +8265,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://careers.wh.org.au/job/General-Practitioner-Custodial-Health/1359743566/</t>
+          <t>https://careers.wh.org.au/job/2027-Emergency-Medicine-Medical-Officer/1361118766/</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -7848,11 +8282,7 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>High Match</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -7860,47 +8290,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Priya Sharma</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RACP</t>
+          <t>Western_Health</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Adult Internal Medicine</t>
+          <t>General Practitioner - Custodial Health</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paediatrics</t>
+          <t>General Practitioner (GP)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>General Practitioner (GP)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>RACP Member Hospital (AU)</t>
+          <t>Western Health</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>nt</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/basic-training/adult-internal-medicine</t>
+          <t>https://careers.wh.org.au/job/General-Practitioner-Custodial-Health/1359743566/</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -7917,7 +8347,11 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7935,7 +8369,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Paediatrics &amp; Child Health</t>
+          <t>Adult Internal Medicine</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -7943,7 +8377,11 @@
           <t>Paediatrics</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -7961,7 +8399,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/basic-training/paediatrics-child-health</t>
+          <t>https://www.racp.edu.au/trainees/basic-training/adult-internal-medicine</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -7996,7 +8434,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Addiction Medicine</t>
+          <t>Paediatrics &amp; Child Health</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -8022,7 +8460,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/addiction-medicine</t>
+          <t>https://www.racp.edu.au/trainees/basic-training/paediatrics-child-health</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -8057,7 +8495,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Adolescent and Young Adult Medicine</t>
+          <t>Addiction Medicine</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -8083,7 +8521,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/adolescent-and-young-adult-medicine</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/addiction-medicine</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -8118,19 +8556,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Post-Fellowship training</t>
+          <t>Adolescent and Young Adult Medicine</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Internal Medicine</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Fellow</t>
-        </is>
-      </c>
+          <t>Paediatrics</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -8148,7 +8582,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/multi-specialty-training-options/post-fellowship-training</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/adolescent-and-young-adult-medicine</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -8165,11 +8599,7 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>High Match</t>
-        </is>
-      </c>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8187,7 +8617,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Post-Fellowship training</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -8217,7 +8647,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/cardiology</t>
+          <t>https://www.racp.edu.au/trainees/multi-specialty-training-options/post-fellowship-training</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -8256,7 +8686,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>New curricula</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -8286,7 +8716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/new-curricula</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/cardiology</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -8325,7 +8755,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Advanced Training - New Curricula</t>
+          <t>New curricula</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -8355,7 +8785,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/recognition-of-prior-learning/advanced-training-new-curricula</t>
+          <t>https://www.racp.edu.au/trainees/new-curricula</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -8384,51 +8814,51 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dr. Priya Sharma</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Monash_Health</t>
+          <t>RACP</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2027 Obstetric &amp; Gynaecology - Senior Registrar</t>
+          <t>Advanced Training - New Curricula</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gynaecology</t>
+          <t>Internal Medicine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Senior Registrar</t>
+          <t>Fellow</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Monash Health</t>
+          <t>RACP Member Hospital (AU)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>nt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://careers.monashhealth.org/job/Clayton-2027-Obstetric-&amp;-Gynaecology-Senior-Registrar-VIC-3168/1362522866/</t>
+          <t>https://www.racp.edu.au/trainees/recognition-of-prior-learning/advanced-training-new-curricula</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -8441,7 +8871,11 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>High Match</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8454,17 +8888,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eastern_Health</t>
+          <t>Monash_Health</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2027 Senior Registrar - Obstetrics &amp; Gynaecology</t>
+          <t>2027 Obstetric &amp; Gynaecology - Senior Registrar</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Obstetrics</t>
+          <t>Gynaecology</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8474,7 +8908,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Eastern Health</t>
+          <t>Monash Health</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -8489,7 +8923,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Senior-Registrar-Obstetrics-&amp;-Gynaecology-VIC-3128/1362270666/</t>
+          <t>https://careers.monashhealth.org/job/Clayton-2027-Obstetric-&amp;-Gynaecology-Senior-Registrar-VIC-3168/1362522866/</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -8514,20 +8948,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Priya Sharma</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monash_Health</t>
+          <t>Eastern_Health</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2027 Intensive Care Registrar and Senior Registrars  - MMC &amp; VHH</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>2027 Senior Registrar - Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Obstetrics</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>Senior Registrar</t>
@@ -8535,7 +8973,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Monash Health</t>
+          <t>Eastern Health</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -8550,15 +8988,15 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://careers.monashhealth.org/job/Clayton-2027-Intensive-Care-Registrar-and-Senior-Registrars-MMC-&amp;-VHH-VIC-3168/1360917466/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Senior-Registrar-Obstetrics-&amp;-Gynaecology-VIC-3128/1362270666/</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Good Match</t>
+          <t>High Match</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -8575,32 +9013,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dr. Priya Sharma</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Western_Health</t>
+          <t>Monash_Health</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2027 Senior Obstetric &amp; Gynaecology Registrars</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Gynaecology</t>
-        </is>
-      </c>
+          <t>2027 Intensive Care Registrar and Senior Registrars  - MMC &amp; VHH</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Senior Registrar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Western Health</t>
+          <t>Monash Health</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -8615,7 +9049,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://careers.wh.org.au/job/2027-Senior-Obstetric-&amp;-Gynaecology-Registrars/1362020866/</t>
+          <t>https://careers.monashhealth.org/job/Clayton-2027-Intensive-Care-Registrar-and-Senior-Registrars-MMC-&amp;-VHH-VIC-3168/1360917466/</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -8645,17 +9079,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Grampians_Health</t>
+          <t>Western_Health</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Registrar - Obstetrics &amp; Gynaecology Unaccredited</t>
+          <t>2027 Senior Obstetric &amp; Gynaecology Registrars</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Obstetrics</t>
+          <t>Gynaecology</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -8665,7 +9099,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Grampians Health</t>
+          <t>Western Health</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -8680,7 +9114,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Obstetrics-&amp;-Gynaecology-Unaccredited-VIC-3350/1357598066/</t>
+          <t>https://careers.wh.org.au/job/2027-Senior-Obstetric-&amp;-Gynaecology-Registrars/1362020866/</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -8715,7 +9149,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Obstetrics &amp; Gynaecology Registrar (Accredited)</t>
+          <t>Registrar - Obstetrics &amp; Gynaecology Unaccredited</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8745,7 +9179,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Obstetrics-&amp;-Gynaecology-Registrar-%28Accredited%29-VIC-3350/1362508966/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Obstetrics-&amp;-Gynaecology-Unaccredited-VIC-3350/1357598066/</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -8770,32 +9204,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. Priya Sharma</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RCH</t>
+          <t>Grampians_Health</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2027 Senior Registrar General Medicine</t>
+          <t>Obstetrics &amp; Gynaecology Registrar (Accredited)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>General Medicine</t>
+          <t>Obstetrics</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Senior Registrar</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Royal Children's Hospital</t>
+          <t>Grampians Health</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -8810,7 +9244,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Senior-Registrar-General-Medicine/1362878366/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Obstetrics-&amp;-Gynaecology-Registrar-%28Accredited%29-VIC-3350/1362508966/</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -8896,28 +9330,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Michael O'Brien</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monash_Health</t>
+          <t>RCH</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2027 Diabetes &amp; Endocrinology Registrar - unaccredited</t>
+          <t>Neurology Consultant</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Monash Health</t>
+          <t>Royal Children's Hospital</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -8932,11 +9366,11 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://careers.monashhealth.org/job/Clayton-2027-Diabetes-&amp;-Endocrinology-Registrar-unaccredited-VIC-3168/1361886666/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Neurology-Consultant/1362944566/</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -11345,7 +11779,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -11379,7 +11812,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>High Match</t>
@@ -11417,7 +11849,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -11451,8 +11882,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -11485,7 +11914,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -11519,8 +11947,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11533,7 +11959,6 @@
           <t>Psychiatry</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -11549,7 +11974,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -11583,8 +12007,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -12122,7 +12544,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -12156,8 +12577,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12170,7 +12589,6 @@
           <t>ICU</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>Grampians Health</t>
@@ -12186,7 +12604,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -12220,8 +12637,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12254,7 +12669,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -12288,8 +12702,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12302,7 +12714,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>Grampians Health</t>
@@ -12318,7 +12729,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -12352,8 +12762,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12386,7 +12794,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -12420,8 +12827,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12429,7 +12834,6 @@
           <t>International Job Seekers</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>Intern</t>
@@ -12450,7 +12854,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -12484,8 +12887,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -13118,7 +13519,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>Eastern Health</t>
@@ -13134,7 +13534,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -13168,8 +13567,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -13177,7 +13574,6 @@
           <t>2027 Upper Gastro Intestinal Research Fellow</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>Fellow</t>
@@ -13198,7 +13594,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -13232,8 +13627,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -13288,11 +13681,11 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. Michael O'Brien</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -13472,7 +13865,7 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
@@ -13597,7 +13990,7 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -13657,7 +14050,7 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -14851,7 +15244,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -14885,7 +15277,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>High Match</t>
@@ -14923,7 +15314,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -14957,7 +15347,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>High Match</t>
@@ -14995,7 +15384,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15029,7 +15417,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>High Match</t>
@@ -15067,7 +15454,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15101,7 +15487,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>High Match</t>
@@ -15119,7 +15504,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -15135,7 +15519,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15169,8 +15552,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -15183,7 +15564,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -15199,7 +15579,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15233,8 +15612,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -15247,7 +15624,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -15263,7 +15639,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15297,8 +15672,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -15311,7 +15684,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -15327,7 +15699,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15361,8 +15732,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -15375,7 +15744,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -15391,7 +15759,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15425,8 +15792,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -15439,7 +15804,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -15455,7 +15819,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15489,8 +15852,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -15523,7 +15884,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15557,8 +15917,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -15591,7 +15949,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15625,8 +15982,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -15659,7 +16014,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15693,8 +16047,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -15727,7 +16079,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15761,8 +16112,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -15795,7 +16144,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15829,8 +16177,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -15863,7 +16209,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15897,8 +16242,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -15931,7 +16274,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -15965,8 +16307,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -15979,7 +16319,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -15995,7 +16334,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -16029,8 +16367,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -16038,7 +16374,6 @@
           <t>International Grants</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
           <t>Intern</t>
@@ -16059,7 +16394,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -16093,8 +16427,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -16102,7 +16434,6 @@
           <t>Prizes, grants, scholarships and fellowships</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
           <t>Fellow</t>
@@ -16123,7 +16454,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -16157,8 +16487,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19328,11 +19656,11 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. Michael O'Brien</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="H63" t="n">
         <v>30</v>
@@ -19482,7 +19810,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="H66" t="n">
         <v>30</v>
@@ -19582,7 +19910,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H68" t="n">
         <v>30</v>
@@ -19632,7 +19960,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="H69" t="n">
         <v>20</v>
@@ -24488,7 +24816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24496,7 +24824,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="47" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -24591,12 +24919,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Grampians_Health</t>
+          <t>RCH</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Registrar - General Medicine Advanced Trainee</t>
+          <t>2027 Senior Registrar General Medicine</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -24606,12 +24934,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Senior Registrar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Grampians Health</t>
+          <t>Royal Children's Hospital</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -24626,11 +24954,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-General-Medicine-Advanced-Trainee-VIC-3350/1362283766/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Senior-Registrar-General-Medicine/1362878366/</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -24661,17 +24989,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fractional Staff Specialist - Endocrinology</t>
+          <t>Registrar - General Medicine Advanced Trainee</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Endocrinology</t>
+          <t>General Medicine</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -24691,15 +25019,15 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Fractional-Staff-Specialist-Endocrinology-VIC-3350/1362736566/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-General-Medicine-Advanced-Trainee-VIC-3350/1362283766/</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Good Match</t>
+          <t>High Match</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -24721,12 +25049,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Monash_Health</t>
+          <t>RCH</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Consultant Paediatrician - Internal Locum</t>
+          <t>Neurology Consultant</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -24737,7 +25065,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Monash Health</t>
+          <t>Royal Children's Hospital</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -24752,15 +25080,15 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://careers.monashhealth.org/job/Clayton-Consultant-Paediatrician-Internal-Locum-VIC-3168/1363118266/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Neurology-Consultant/1362944566/</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Partial Match</t>
+          <t>Good Match</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -24782,15 +25110,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RCH</t>
+          <t>Grampians_Health</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Neurology Consultant</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Fractional Staff Specialist - Endocrinology</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Endocrinology</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Consultant</t>
@@ -24798,7 +25130,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Royal Children's Hospital</t>
+          <t>Grampians Health</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -24813,15 +25145,15 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Neurology-Consultant/1362944566/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Fractional-Staff-Specialist-Endocrinology-VIC-3350/1362736566/</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Partial Match</t>
+          <t>Good Match</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -24843,12 +25175,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Grampians_Health</t>
+          <t>Monash_Health</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stawell - Consultant Anaesthetist</t>
+          <t>Consultant Paediatrician - Internal Locum</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -24859,7 +25191,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Grampians Health</t>
+          <t>Monash Health</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -24874,11 +25206,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Stawell-Stawell-Consultant-Anaesthetist-VIC-3380/1363307366/</t>
+          <t>https://careers.monashhealth.org/job/Clayton-Consultant-Paediatrician-Internal-Locum-VIC-3168/1363118266/</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -24909,13 +25241,13 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>International Job Seekers</t>
+          <t>Stawell - Consultant Anaesthetist</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -24935,15 +25267,15 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.gh.org.au/careers-and-training/international-recruitment/</t>
+          <t>https://careers.grampianshealth.com/job/Stawell-Stawell-Consultant-Anaesthetist-VIC-3380/1363307366/</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Low Match</t>
+          <t>Partial Match</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -24965,12 +25297,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RACP</t>
+          <t>Grampians_Health</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>International Grants</t>
+          <t>International Job Seekers</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -24981,22 +25313,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>RACP Member Hospital (AU)</t>
+          <t>Grampians Health</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>nt</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/foundation/international-grants</t>
+          <t>https://www.gh.org.au/careers-and-training/international-recruitment/</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -25014,6 +25346,67 @@
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dr. Michael O'Brien</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RACP</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>International Grants</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RACP Member Hospital (AU)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>nt</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://www.racp.edu.au/foundation/international-grants</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>28</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Low Match</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25026,22 +25419,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
@@ -25117,71 +25510,6 @@
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Dr. Sarah Williams</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>RCH</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2027 Senior Registrar General Medicine</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>General Medicine</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Senior Registrar</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Royal Children's Hospital</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>VIC</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>VIC</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Senior-Registrar-General-Medicine/1362878366/</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>69</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Good Match</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27446,7 +27774,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -27480,7 +27807,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>High Match</t>
@@ -27518,7 +27844,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -27552,8 +27877,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27586,7 +27909,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -27620,8 +27942,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27634,7 +27954,6 @@
           <t>Psychiatry</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -27650,7 +27969,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>29-06-2026</t>
@@ -27684,8 +28002,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Job_Tracker.xlsx
+++ b/Job_Tracker.xlsx
@@ -722,7 +722,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -771,7 +770,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>Fuzzy title match</t>
@@ -809,7 +807,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -854,8 +851,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -888,7 +883,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -937,7 +931,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -950,7 +943,6 @@
           <t>Registrar - Surgical Plastics (Unaccredited)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -971,7 +963,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -1020,7 +1011,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -1058,7 +1048,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -1107,7 +1096,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -1145,7 +1133,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -1194,7 +1181,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -1207,7 +1193,6 @@
           <t>Stawell - Consultant Anaesthetist</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Consultant</t>
@@ -1228,7 +1213,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -1277,7 +1261,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -1315,7 +1298,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -1364,7 +1346,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -1402,7 +1383,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -1451,7 +1431,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -1469,7 +1448,6 @@
           <t>ICU</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>Grampians Health</t>
@@ -1485,7 +1463,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -1534,7 +1511,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -1552,7 +1528,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>Grampians Health</t>
@@ -1568,7 +1543,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -1617,7 +1591,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -1655,7 +1628,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -1704,7 +1676,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -1717,7 +1688,6 @@
           <t>International Job Seekers</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Intern</t>
@@ -1738,7 +1708,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -1787,7 +1756,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -1825,7 +1793,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -1874,7 +1841,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -2044,7 +2010,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -2089,8 +2054,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2123,7 +2086,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -2172,7 +2134,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -2185,7 +2146,6 @@
           <t>2026 Paediatric Registrar (August 2026)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -2206,7 +2166,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -2255,7 +2214,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -2293,7 +2251,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -2342,7 +2299,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -2380,7 +2336,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -2429,7 +2384,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -2442,7 +2396,6 @@
           <t>2027 General Surgical Registrar (Un-Accredited)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -2463,7 +2416,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -2512,7 +2464,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -2550,7 +2501,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -2599,7 +2549,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -2612,7 +2561,6 @@
           <t>2026 Addiction Medicine Registrar</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -2633,7 +2581,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -2682,7 +2629,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -2695,7 +2641,6 @@
           <t>2027 Addiction Medicine Registrar</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -2716,7 +2661,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -2765,7 +2709,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -2778,7 +2721,6 @@
           <t>2027 Plastic Surgery Unaccredited Registrar</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -2799,7 +2741,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -2848,7 +2789,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -2861,7 +2801,6 @@
           <t>2027 Upper Gastro Intestinal Research Fellow</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Fellow</t>
@@ -2882,7 +2821,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -2931,7 +2869,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -3101,7 +3038,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -3150,7 +3086,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -3163,7 +3098,6 @@
           <t>2027 Paediatric Registrars VPAT (Advanced and Continuing Trainees)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -3184,7 +3118,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -3233,7 +3166,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -3271,7 +3203,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -3320,7 +3251,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -3358,7 +3288,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -3407,7 +3336,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -3420,7 +3348,6 @@
           <t>Microbiology Registrar 2027</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -3441,7 +3368,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -3490,7 +3416,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -3503,7 +3428,6 @@
           <t>2027 Allergy &amp; Immunology Fellow / Registrar</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -3524,7 +3448,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -3573,7 +3496,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -3611,7 +3533,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -3660,7 +3581,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -3962,7 +3882,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -4011,7 +3930,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -4049,7 +3967,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -4098,7 +4015,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -4136,7 +4052,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -4185,7 +4100,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -4223,7 +4137,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -4272,7 +4185,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -4310,7 +4222,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -4359,7 +4270,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -4397,7 +4307,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -4446,7 +4355,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -4484,7 +4392,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -4533,7 +4440,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -4571,7 +4477,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -4620,7 +4525,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -4633,7 +4537,6 @@
           <t>Prizes, grants, scholarships and fellowships</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Fellow</t>
@@ -4654,7 +4557,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -4703,7 +4605,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -4721,7 +4622,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -4737,7 +4637,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -4786,7 +4685,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -4824,7 +4722,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -4873,7 +4770,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -4891,7 +4787,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -4907,7 +4802,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -4956,7 +4850,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -4994,7 +4887,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -5043,7 +4935,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -5081,7 +4972,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -5130,7 +5020,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -5168,7 +5057,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -5217,7 +5105,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -5235,7 +5122,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -5251,7 +5137,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -5300,7 +5185,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -5338,7 +5222,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -5387,7 +5270,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -5405,7 +5287,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -5421,7 +5302,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -5470,7 +5350,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -5488,7 +5367,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -5504,7 +5382,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -5553,7 +5430,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -5591,7 +5467,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -5640,7 +5515,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -5653,7 +5527,6 @@
           <t>International Grants</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>Intern</t>
@@ -5674,7 +5547,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -5723,7 +5595,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -5741,7 +5612,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -5757,7 +5627,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -5806,7 +5675,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -5824,7 +5692,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -5840,7 +5707,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -5889,7 +5755,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -5927,7 +5792,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -5976,7 +5840,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -6258,7 +6121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9470,6 +9333,534 @@
         <v>0</v>
       </c>
       <c r="G97" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SmartJobs_QLD</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Jobs_NT</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Careers_VIC</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Monash_Health</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>23</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Western_Health</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>16</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>WA_Health</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>24</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Peninsula_Health</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>The_Womens</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Grampians_Health</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>14</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Eastern_Health</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>11</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>7</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>RANZCOG</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>RACP</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>24</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>JobRadars</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>PageUp</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Mercy_Workday</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="inlineStr">
         <is>
           <t>all_methods_failed</t>
         </is>
@@ -11723,7 +12114,6 @@
           <t>Registrar - Medical Administration 2027</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -11744,7 +12134,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -11793,7 +12182,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -11806,7 +12194,6 @@
           <t>Registrar (Medical, Family Property and Defamation Lists)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -11827,7 +12214,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -11876,7 +12262,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -11914,7 +12299,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -11963,7 +12347,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -12001,7 +12384,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -12046,8 +12428,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12060,7 +12440,6 @@
           <t>Internal Medicine</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>Monash Health</t>
@@ -12076,7 +12455,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -12125,7 +12503,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -12163,7 +12540,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -12212,7 +12588,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -12250,7 +12625,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -12299,7 +12673,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -12312,7 +12685,6 @@
           <t>Consultant Paediatrician - Internal Locum</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Consultant</t>
@@ -12333,7 +12705,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -12382,7 +12753,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -12395,7 +12765,6 @@
           <t>2027 Medical Administration Registrar</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -12416,7 +12785,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -12465,7 +12833,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -12478,7 +12845,6 @@
           <t>2026 Anaesthetic Registrar</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -12499,7 +12865,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -12548,7 +12913,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -12561,7 +12925,6 @@
           <t>Consultant Paediatrician - Infectious Diseases Intenal Locum</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Consultant</t>
@@ -12582,7 +12945,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -12631,7 +12993,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -12669,7 +13030,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -12718,7 +13078,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -12756,7 +13115,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -12805,7 +13163,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -12843,7 +13200,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -12892,7 +13248,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -12905,7 +13260,6 @@
           <t>2027 Obesity, Clinical Nutrition &amp; Diabetes Clinical Registrar</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -12926,7 +13280,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -12975,7 +13328,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -12988,7 +13340,6 @@
           <t>Consultant Paediatrician</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>Consultant</t>
@@ -13009,7 +13360,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -13058,7 +13408,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -13096,7 +13445,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -13145,7 +13493,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -13183,7 +13530,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -13232,7 +13578,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -13245,7 +13590,6 @@
           <t>2027 Neonatal Medical Officer</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>Medical Officer</t>
@@ -13266,7 +13610,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -13315,7 +13658,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -13328,7 +13670,6 @@
           <t>2027 Fellow (ATR) - Paediatrician in School</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>Fellow</t>
@@ -13349,7 +13690,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -13398,7 +13738,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -13416,7 +13755,6 @@
           <t>Psychiatry</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>Monash Health</t>
@@ -13432,7 +13770,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -13481,7 +13818,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -13499,7 +13835,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>Monash Health</t>
@@ -13515,7 +13850,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -13564,7 +13898,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -13577,7 +13910,6 @@
           <t>2027 Upper GI/HPB Surgery Clinical Fellow</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>Fellow</t>
@@ -13598,7 +13930,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -13647,7 +13978,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -13685,7 +14015,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -13734,7 +14063,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -13752,7 +14080,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>Monash Health</t>
@@ -13768,7 +14095,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -13817,7 +14143,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -13830,7 +14155,6 @@
           <t>2027 Education Fellow</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>Fellow</t>
@@ -13851,7 +14175,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -13900,7 +14223,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -13938,7 +14260,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -13987,7 +14308,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>Experience level mismatch</t>
@@ -14005,7 +14325,6 @@
           <t>Emergency Medicine</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -14021,7 +14340,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -14070,7 +14388,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -14108,7 +14425,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -14157,7 +14473,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -14170,7 +14485,6 @@
           <t>2027 Paediatric Chief Registrar</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -14191,7 +14505,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -14240,7 +14553,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -14253,7 +14565,6 @@
           <t>2027 Hospital Medical Officer (PGY2)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>Medical Officer</t>
@@ -14274,7 +14585,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -14323,7 +14633,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -14336,7 +14645,6 @@
           <t>2027 Hospital Medical Officer (BPT2)</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>Medical Officer</t>
@@ -14357,7 +14665,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -14406,7 +14713,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -14419,7 +14725,6 @@
           <t>Hospital Medical Officer - August 2026+</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>Medical Officer</t>
@@ -14440,7 +14745,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -14489,7 +14793,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -14527,7 +14830,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -14576,7 +14878,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -14594,7 +14895,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -14610,7 +14910,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -14659,7 +14958,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -14697,7 +14995,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -14746,7 +15043,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -14784,7 +15080,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -14833,7 +15128,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -14851,7 +15145,6 @@
           <t>Gastroenterology</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -14867,7 +15160,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -14916,7 +15208,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -14934,7 +15225,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -14950,7 +15240,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -14999,7 +15288,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -15017,7 +15305,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -15033,7 +15320,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -15082,7 +15368,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -15100,7 +15385,6 @@
           <t>Psychiatry</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -15116,7 +15400,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -15165,7 +15448,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -15183,7 +15465,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -15199,7 +15480,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -15248,7 +15528,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -15266,7 +15545,6 @@
           <t>Emergency Medicine</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>WA Health</t>
@@ -15282,7 +15560,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -15331,7 +15608,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>Fuzzy title match; Experience level mismatch</t>
@@ -15369,7 +15645,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -15418,7 +15693,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -15456,7 +15730,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -15505,7 +15778,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -15543,7 +15815,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -15592,7 +15863,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>Weak title relevance; Location mismatch; Experience level mismatch</t>
@@ -15630,7 +15900,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -15679,7 +15948,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>Weak title relevance; Location mismatch; Experience level mismatch</t>
@@ -15717,7 +15985,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -15766,7 +16033,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -15804,7 +16070,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -15853,7 +16118,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -15891,7 +16155,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -15940,7 +16203,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -15978,7 +16240,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -16027,7 +16288,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -16040,7 +16300,6 @@
           <t>Senior Registrar - Medical Education</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>Senior Registrar</t>
@@ -16061,7 +16320,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -16110,7 +16368,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>Specialty mismatch; Location mismatch</t>
@@ -16123,7 +16380,6 @@
           <t>Registrar - Service - Medical Education</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -16144,7 +16400,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -16193,7 +16448,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -16206,7 +16460,6 @@
           <t>Registrar - Trainee/Service - Rehabilitation Medicine</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -16227,7 +16480,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -16276,7 +16528,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -16314,7 +16565,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -16363,7 +16613,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -16401,7 +16650,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -16450,7 +16698,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -16463,7 +16710,6 @@
           <t>Senior Registrar - Surgical Education</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>Senior Registrar</t>
@@ -16484,7 +16730,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -16533,7 +16778,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -16571,7 +16815,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -16620,7 +16863,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -16658,7 +16900,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -16707,7 +16948,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -16745,7 +16985,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -16794,7 +17033,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -16832,7 +17070,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -16881,7 +17118,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -16919,7 +17155,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -16968,7 +17203,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -16981,7 +17215,6 @@
           <t>Fellow - Endocrine Surgery</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>Senior Registrar</t>
@@ -17002,7 +17235,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -17051,7 +17283,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -17089,7 +17320,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -17138,7 +17368,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -17176,7 +17405,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -17225,7 +17453,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -17263,7 +17490,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -17312,7 +17538,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -17350,7 +17575,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -17395,8 +17619,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17429,7 +17651,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -17478,7 +17699,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
           <t>Fuzzy title match</t>
@@ -17516,7 +17736,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -17561,8 +17780,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -17595,7 +17812,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -17644,7 +17860,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -17657,7 +17872,6 @@
           <t>Registrar - Surgical Plastics (Unaccredited)</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -17678,7 +17892,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -17727,7 +17940,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -17765,7 +17977,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -17814,7 +18025,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -17852,7 +18062,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -17901,7 +18110,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -17914,7 +18122,6 @@
           <t>Stawell - Consultant Anaesthetist</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
           <t>Consultant</t>
@@ -17935,7 +18142,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -17984,7 +18190,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -18022,7 +18227,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -18071,7 +18275,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -18109,7 +18312,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -18158,7 +18360,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -18176,7 +18377,6 @@
           <t>ICU</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>Grampians Health</t>
@@ -18192,7 +18392,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -18241,7 +18440,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -18259,7 +18457,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>Grampians Health</t>
@@ -18275,7 +18472,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -18324,7 +18520,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -18362,7 +18557,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -18411,7 +18605,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -18424,7 +18617,6 @@
           <t>International Job Seekers</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
           <t>Intern</t>
@@ -18445,7 +18637,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -18494,7 +18685,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -18532,7 +18722,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -18581,7 +18770,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -18619,7 +18807,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -18664,8 +18851,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -18698,7 +18883,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -18747,7 +18931,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -18760,7 +18943,6 @@
           <t>2026 Paediatric Registrar (August 2026)</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -18781,7 +18963,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -18830,7 +19011,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -18868,7 +19048,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -18917,7 +19096,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -18955,7 +19133,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -19004,7 +19181,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -19017,7 +19193,6 @@
           <t>2027 General Surgical Registrar (Un-Accredited)</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -19038,7 +19213,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -19087,7 +19261,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -19125,7 +19298,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -19174,7 +19346,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -19187,7 +19358,6 @@
           <t>2026 Addiction Medicine Registrar</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -19208,7 +19378,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -19257,7 +19426,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -19270,7 +19438,6 @@
           <t>2027 Addiction Medicine Registrar</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -19291,7 +19458,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -19340,7 +19506,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -19353,7 +19518,6 @@
           <t>2027 Plastic Surgery Unaccredited Registrar</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -19374,7 +19538,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -19423,7 +19586,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -19436,7 +19598,6 @@
           <t>2027 Upper Gastro Intestinal Research Fellow</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
           <t>Fellow</t>
@@ -19457,7 +19618,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -19506,7 +19666,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -19544,7 +19703,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -19593,7 +19751,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -19606,7 +19763,6 @@
           <t>2027 Paediatric Registrars VPAT (Advanced and Continuing Trainees)</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -19627,7 +19783,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -19676,7 +19831,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -19714,7 +19868,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -19763,7 +19916,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -19801,7 +19953,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -19850,7 +20001,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -19863,7 +20013,6 @@
           <t>Microbiology Registrar 2027</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -19884,7 +20033,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -19933,7 +20081,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -19946,7 +20093,6 @@
           <t>2027 Allergy &amp; Immunology Fellow / Registrar</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -19967,7 +20113,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -20016,7 +20161,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -20054,7 +20198,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -20103,7 +20246,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -20141,7 +20283,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -20190,7 +20331,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -20228,7 +20368,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -20277,7 +20416,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -20315,7 +20453,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -20364,7 +20501,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -20402,7 +20538,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -20451,7 +20586,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -20489,7 +20623,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -20538,7 +20671,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -20576,7 +20708,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -20625,7 +20756,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -20663,7 +20793,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -20712,7 +20841,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -20750,7 +20878,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -20799,7 +20926,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -20812,7 +20938,6 @@
           <t>Prizes, grants, scholarships and fellowships</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
           <t>Fellow</t>
@@ -20833,7 +20958,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -20882,7 +21006,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -20900,7 +21023,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -20916,7 +21038,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -20965,7 +21086,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -21003,7 +21123,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -21052,7 +21171,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -21070,7 +21188,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -21086,7 +21203,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -21135,7 +21251,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -21173,7 +21288,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -21222,7 +21336,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -21260,7 +21373,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -21309,7 +21421,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -21347,7 +21458,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -21396,7 +21506,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -21414,7 +21523,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -21430,7 +21538,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -21479,7 +21586,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -21517,7 +21623,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -21566,7 +21671,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -21584,7 +21688,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -21600,7 +21703,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -21649,7 +21751,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -21667,7 +21768,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -21683,7 +21783,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -21732,7 +21831,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -21770,7 +21868,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -21819,7 +21916,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -21832,7 +21928,6 @@
           <t>International Grants</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
           <t>Intern</t>
@@ -21853,7 +21948,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -21902,7 +21996,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -21920,7 +22013,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -21936,7 +22028,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -21985,7 +22076,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -22003,7 +22093,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -22019,7 +22108,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -22068,7 +22156,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -22106,7 +22193,6 @@
           <t>NT</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -22155,7 +22241,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -34490,7 +34575,6 @@
           <t>Registrar - Medical Administration 2027</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -34511,7 +34595,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -34560,7 +34643,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -34573,7 +34655,6 @@
           <t>Registrar (Medical, Family Property and Defamation Lists)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -34594,7 +34675,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -34643,7 +34723,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -34681,7 +34760,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -34730,7 +34808,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -34900,7 +34977,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -34945,8 +35021,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34959,7 +35033,6 @@
           <t>Internal Medicine</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Monash Health</t>
@@ -34975,7 +35048,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -35024,7 +35096,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -35062,7 +35133,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -35111,7 +35181,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -35149,7 +35218,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -35198,7 +35266,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -35211,7 +35278,6 @@
           <t>Consultant Paediatrician - Internal Locum</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Consultant</t>
@@ -35232,7 +35298,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -35281,7 +35346,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -35294,7 +35358,6 @@
           <t>2027 Medical Administration Registrar</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -35315,7 +35378,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -35364,7 +35426,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -35377,7 +35438,6 @@
           <t>2026 Anaesthetic Registrar</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -35398,7 +35458,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -35447,7 +35506,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -35460,7 +35518,6 @@
           <t>Consultant Paediatrician - Infectious Diseases Intenal Locum</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Consultant</t>
@@ -35481,7 +35538,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -35530,7 +35586,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -35568,7 +35623,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -35617,7 +35671,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -35655,7 +35708,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -35704,7 +35756,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -35742,7 +35793,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -35791,7 +35841,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -35804,7 +35853,6 @@
           <t>2027 Obesity, Clinical Nutrition &amp; Diabetes Clinical Registrar</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -35825,7 +35873,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -35874,7 +35921,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -35887,7 +35933,6 @@
           <t>Consultant Paediatrician</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Consultant</t>
@@ -35908,7 +35953,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -35957,7 +36001,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -35995,7 +36038,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -36044,7 +36086,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -36082,7 +36123,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -36131,7 +36171,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -36144,7 +36183,6 @@
           <t>2027 Neonatal Medical Officer</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>Medical Officer</t>
@@ -36165,7 +36203,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -36214,7 +36251,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -36227,7 +36263,6 @@
           <t>2027 Fellow (ATR) - Paediatrician in School</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>Fellow</t>
@@ -36248,7 +36283,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -36297,7 +36331,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -36315,7 +36348,6 @@
           <t>Psychiatry</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>Monash Health</t>
@@ -36331,7 +36363,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -36380,7 +36411,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -36398,7 +36428,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>Monash Health</t>
@@ -36414,7 +36443,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -36463,7 +36491,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -36476,7 +36503,6 @@
           <t>2027 Upper GI/HPB Surgery Clinical Fellow</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>Fellow</t>
@@ -36497,7 +36523,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -36546,7 +36571,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -36584,7 +36608,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -36633,7 +36656,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -36651,7 +36673,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>Monash Health</t>
@@ -36667,7 +36688,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -36716,7 +36736,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -36729,7 +36748,6 @@
           <t>2027 Education Fellow</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>Fellow</t>
@@ -36750,7 +36768,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -36799,7 +36816,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -36969,7 +36985,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -37018,7 +37033,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>Experience level mismatch</t>
@@ -37036,7 +37050,6 @@
           <t>Emergency Medicine</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -37052,7 +37065,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -37101,7 +37113,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -37139,7 +37150,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -37188,7 +37198,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -37201,7 +37210,6 @@
           <t>2027 Paediatric Chief Registrar</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -37222,7 +37230,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -37271,7 +37278,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -37284,7 +37290,6 @@
           <t>2027 Hospital Medical Officer (PGY2)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Medical Officer</t>
@@ -37305,7 +37310,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -37354,7 +37358,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -37367,7 +37370,6 @@
           <t>2027 Hospital Medical Officer (BPT2)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Medical Officer</t>
@@ -37388,7 +37390,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -37437,7 +37438,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -37450,7 +37450,6 @@
           <t>Hospital Medical Officer - August 2026+</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Medical Officer</t>
@@ -37471,7 +37470,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -37520,7 +37518,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -37558,7 +37555,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -37607,7 +37603,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -37625,7 +37620,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -37641,7 +37635,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -37690,7 +37683,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -37728,7 +37720,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -37777,7 +37768,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -37815,7 +37805,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -37864,7 +37853,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -37882,7 +37870,6 @@
           <t>Gastroenterology</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -37898,7 +37885,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -37947,7 +37933,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -37965,7 +37950,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -37981,7 +37965,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -38030,7 +38013,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -38048,7 +38030,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -38064,7 +38045,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -38113,7 +38093,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -38131,7 +38110,6 @@
           <t>Psychiatry</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -38147,7 +38125,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -38196,7 +38173,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -38214,7 +38190,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -38230,7 +38205,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -38279,7 +38253,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -38429,7 +38402,6 @@
           <t>Emergency Medicine</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>WA Health</t>
@@ -38445,7 +38417,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -38494,7 +38465,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>Fuzzy title match; Experience level mismatch</t>
@@ -38532,7 +38502,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -38581,7 +38550,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -38619,7 +38587,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -38668,7 +38635,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>Weak title relevance; Experience level mismatch</t>
@@ -38706,7 +38672,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -38755,7 +38720,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>Weak title relevance; Location mismatch; Experience level mismatch</t>
@@ -38793,7 +38757,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -38842,7 +38805,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>Weak title relevance; Location mismatch; Experience level mismatch</t>
@@ -38880,7 +38842,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -38929,7 +38890,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -38967,7 +38927,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -39016,7 +38975,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -39054,7 +39012,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -39103,7 +39060,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -39141,7 +39097,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -39190,7 +39145,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -39203,7 +39157,6 @@
           <t>Senior Registrar - Medical Education</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Senior Registrar</t>
@@ -39224,7 +39177,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -39273,7 +39225,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>Specialty mismatch; Location mismatch</t>
@@ -39286,7 +39237,6 @@
           <t>Registrar - Service - Medical Education</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -39307,7 +39257,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -39356,7 +39305,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -39369,7 +39317,6 @@
           <t>Registrar - Trainee/Service - Rehabilitation Medicine</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -39390,7 +39337,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -39439,7 +39385,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -39477,7 +39422,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -39526,7 +39470,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -39564,7 +39507,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -39613,7 +39555,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -39626,7 +39567,6 @@
           <t>Senior Registrar - Surgical Education</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Senior Registrar</t>
@@ -39647,7 +39587,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -39696,7 +39635,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -39734,7 +39672,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -39783,7 +39720,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -39821,7 +39757,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -39870,7 +39805,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -39908,7 +39842,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -39957,7 +39890,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -39995,7 +39927,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -40044,7 +39975,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -40082,7 +40012,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -40131,7 +40060,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -40144,7 +40072,6 @@
           <t>Fellow - Endocrine Surgery</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>Senior Registrar</t>
@@ -40165,7 +40092,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -40214,7 +40140,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -40252,7 +40177,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -40301,7 +40225,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -40339,7 +40262,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -40388,7 +40310,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -40426,7 +40347,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -40475,7 +40395,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
@@ -40909,7 +40828,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>30-06-2026</t>
@@ -40954,8 +40872,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Job_Tracker.xlsx
+++ b/Job_Tracker.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -589,7 +589,7 @@
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
   </cols>
@@ -767,7 +767,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -848,7 +848,7 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1838,12 +1838,99 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Registrar - Psychiatry</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Psychiatry</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Registrar</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Grampians Health</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>02-07-2026 09:22</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Psychiatry-VIC-3350/1362426866/</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Grampians_Health</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Dr. Ananya Patel</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>36</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Primary — configured method</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2138,7 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2218,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2211,7 +2298,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2296,7 +2383,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2381,7 +2468,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2461,7 +2548,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -2546,7 +2633,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -2626,7 +2713,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2706,7 +2793,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -2786,7 +2873,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -2866,7 +2953,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2905,7 +2992,7 @@
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="49" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="49" customWidth="1" min="19" max="19"/>
   </cols>
@@ -3083,7 +3170,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3163,7 +3250,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3248,7 +3335,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3333,7 +3420,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3413,7 +3500,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3493,7 +3580,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3578,7 +3665,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3618,7 +3705,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>01-07-2026</t>
@@ -3664,10 +3750,9 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
       <c r="S9" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -4014,7 +4099,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4099,7 +4184,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4184,7 +4269,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4269,7 +4354,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4354,7 +4439,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4439,7 +4524,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -4524,7 +4609,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -4609,7 +4694,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -4689,7 +4774,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4769,7 +4854,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -4854,7 +4939,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -4934,7 +5019,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -5019,7 +5104,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -5104,7 +5189,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -5189,7 +5274,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -5269,7 +5354,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -5354,7 +5439,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -5434,7 +5519,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -5514,7 +5599,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -5599,7 +5684,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -5679,7 +5764,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -5759,7 +5844,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -5839,7 +5924,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -5924,7 +6009,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -6208,7 +6293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10476,6 +10561,534 @@
         <v>0</v>
       </c>
       <c r="G129" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SmartJobs_QLD</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Jobs_NT</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Careers_VIC</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>3</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Monash_Health</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>24</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Western_Health</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>18</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>WA_Health</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" t="n">
+        <v>25</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Peninsula_Health</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>The_Womens</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Grampians_Health</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" t="n">
+        <v>15</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Eastern_Health</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>11</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>8</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>RANZCOG</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>RACP</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="n">
+        <v>24</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>JobRadars</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>PageUp</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Mercy_Workday</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="inlineStr">
         <is>
           <t>all_methods_failed</t>
         </is>
@@ -10656,7 +11269,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -10736,7 +11349,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -10812,7 +11425,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -10888,7 +11501,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -10964,7 +11577,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -11040,7 +11653,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -11124,7 +11737,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -11204,7 +11817,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -11288,7 +11901,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -11372,7 +11985,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -11456,7 +12069,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -11540,7 +12153,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -11624,7 +12237,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
@@ -11708,7 +12321,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
@@ -11792,7 +12405,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -11876,7 +12489,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
@@ -11960,7 +12573,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
@@ -12040,7 +12653,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -12120,7 +12733,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
@@ -12204,7 +12817,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
@@ -12307,7 +12920,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
     </row>
@@ -12344,7 +12957,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
     </row>
@@ -12381,7 +12994,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
     </row>
@@ -12418,7 +13031,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
     </row>
@@ -12455,7 +13068,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
     </row>
@@ -12602,7 +13215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S128"/>
+  <dimension ref="A1:S130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -12794,7 +13407,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -12874,7 +13487,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -12959,7 +13572,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -13040,7 +13653,7 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -13115,7 +13728,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -13200,7 +13813,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -13285,7 +13898,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -13365,7 +13978,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -13445,7 +14058,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -13525,7 +14138,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -13605,7 +14218,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -13690,7 +14303,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -13775,7 +14388,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -13860,7 +14473,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -13940,7 +14553,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -14020,7 +14633,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -14105,7 +14718,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -14190,7 +14803,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -14270,7 +14883,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -14350,7 +14963,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -14430,7 +15043,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -14510,7 +15123,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -14590,7 +15203,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -14675,7 +15288,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -14755,7 +15368,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -14835,7 +15448,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -14850,7 +15463,6 @@
           <t>2027 Rheumatology Registrar  - Unaccredited</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -14871,7 +15483,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>01-07-2026</t>
@@ -14917,10 +15528,9 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -15003,7 +15613,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -15083,7 +15693,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -15168,7 +15778,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -15248,7 +15858,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -15328,7 +15938,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -15408,7 +16018,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -15488,7 +16098,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -15573,7 +16183,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -15653,7 +16263,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -15738,7 +16348,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -15823,7 +16433,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -15903,7 +16513,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -15983,7 +16593,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -16063,7 +16673,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -16143,7 +16753,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -16223,7 +16833,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -16238,7 +16848,6 @@
           <t>2026 Paediatric Emergency Registrar</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -16259,7 +16868,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>01-07-2026</t>
@@ -16305,10 +16913,9 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
       <c r="S45" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -16321,7 +16928,6 @@
           <t>2027 Unaccredited Geriatric Medicine Registrar</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -16342,7 +16948,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>01-07-2026</t>
@@ -16388,10 +16993,9 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -16469,7 +17073,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -16554,7 +17158,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -16639,7 +17243,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -16724,7 +17328,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -16809,7 +17413,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -16894,7 +17498,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -16979,7 +17583,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -17064,7 +17668,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -17149,7 +17753,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -17229,7 +17833,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -17309,7 +17913,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -17389,7 +17993,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -17474,7 +18078,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -17559,7 +18163,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -17639,7 +18243,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -17724,7 +18328,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -17809,7 +18413,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -17894,7 +18498,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -17979,7 +18583,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -18064,7 +18668,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -18144,7 +18748,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -18229,7 +18833,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -18314,7 +18918,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -18399,7 +19003,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -18411,12 +19015,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2027 O&amp;G Senior Registrar</t>
+          <t>Fellow - Trauma Surgery</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Obstetrics &amp; Gynaecology</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -18426,37 +19030,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>The Royal Women's Hospital</t>
+          <t>WA Health</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>VIC</t>
-        </is>
-      </c>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>30-06-2026 21:27</t>
+          <t>02-07-2026 09:22</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>https://careers.thewomens.org.au/job/2027-O&amp;amp;G-Senior-Registrar/2053-en_GB</t>
+          <t>https://medcareerswa.health.wa.gov.au/jobs/fellow-trauma-surgery-royal-perth-hospital-wa-australia-62611f69-14e4-407c-8c70-27588eb003f2</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>The_Womens</t>
+          <t>WA_Health</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -18465,7 +19070,7 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -18474,20 +19079,30 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Fallback — used after primary (static) returned 0 jobs</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr"/>
+          <t>Primary — configured method</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
+        </is>
+      </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Obstetrics &amp; Gynaecology Registrar (Accredited)</t>
+          <t>2027 O&amp;G Senior Registrar</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -18497,12 +19112,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Senior Registrar</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Grampians Health</t>
+          <t>The Royal Women's Hospital</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -18527,12 +19142,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Obstetrics-&amp;-Gynaecology-Registrar-%28Accredited%29-VIC-3350/1362508966/</t>
+          <t>https://careers.thewomens.org.au/job/2027-O&amp;amp;G-Senior-Registrar/2053-en_GB</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Grampians_Health</t>
+          <t>The_Womens</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -18541,38 +19156,29 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>static_html</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Primary — configured method</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Fuzzy title match</t>
-        </is>
-      </c>
+          <t>Fallback — used after primary (static) returned 0 jobs</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>1 day old</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>Fuzzy title match</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Registrar - Obstetrics &amp; Gynaecology Unaccredited</t>
+          <t>Obstetrics &amp; Gynaecology Registrar (Accredited)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -18612,7 +19218,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Obstetrics-&amp;-Gynaecology-Unaccredited-VIC-3350/1357598066/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Obstetrics-&amp;-Gynaecology-Registrar-%28Accredited%29-VIC-3350/1362508966/</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -18626,7 +19232,7 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -18638,22 +19244,31 @@
           <t>Primary — configured method</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Fuzzy title match</t>
+        </is>
+      </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Fuzzy title match</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Registrar - General Medicine Advanced Trainee</t>
+          <t>Registrar - Obstetrics &amp; Gynaecology Unaccredited</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Internal Medicine</t>
+          <t>Obstetrics &amp; Gynaecology</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -18688,7 +19303,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-General-Medicine-Advanced-Trainee-VIC-3350/1362283766/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Obstetrics-&amp;-Gynaecology-Unaccredited-VIC-3350/1357598066/</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -18698,11 +19313,11 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Dr. Michael O'Brien</t>
+          <t>Dr. Priya Sharma</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -18714,26 +19329,22 @@
           <t>Primary — configured method</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Weak title relevance; Experience level mismatch</t>
-        </is>
-      </c>
+      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>1 day old</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>Weak title relevance; Experience level mismatch</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Registrar - Surgical Plastics (Unaccredited)</t>
+          <t>Registrar - General Medicine Advanced Trainee</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Internal Medicine</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -18768,7 +19379,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Surgical-Plastics-%28Unaccredited%29-VIC-3350/1362050466/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-General-Medicine-Advanced-Trainee-VIC-3350/1362283766/</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -18778,11 +19389,11 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Michael O'Brien</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
@@ -18796,29 +19407,24 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch</t>
+          <t>Weak title relevance; Experience level mismatch</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch</t>
+          <t>Weak title relevance; Experience level mismatch</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2027 General Surgery Registrar -Unaccredited</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>General Surgery</t>
+          <t>Registrar - Surgical Plastics (Unaccredited)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -18853,7 +19459,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-2027-General-Surgery-Registrar-Unaccredited-VIC-3350/1362049866/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Surgical-Plastics-%28Unaccredited%29-VIC-3350/1362050466/</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -18867,7 +19473,7 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -18886,7 +19492,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -18898,12 +19504,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Registrar - Urology Unaccredited</t>
+          <t>2027 General Surgery Registrar -Unaccredited</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Urology</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -18938,7 +19544,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Urology-Unaccredited-VIC-3350/1362036766/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-2027-General-Surgery-Registrar-Unaccredited-VIC-3350/1362049866/</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -18952,7 +19558,7 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -18971,7 +19577,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -18983,12 +19589,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Stawell - Consultant Anaesthetist</t>
+          <t>Registrar - Urology Unaccredited</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Urology</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -19018,7 +19629,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Stawell-Stawell-Consultant-Anaesthetist-VIC-3380/1363307366/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Urology-Unaccredited-VIC-3350/1362036766/</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -19028,11 +19639,11 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Dr. Michael O'Brien</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
@@ -19051,7 +19662,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -19063,12 +19674,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Fractional Staff Specialist - Endocrinology</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Endocrinology</t>
+          <t>Stawell - Consultant Anaesthetist</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -19103,7 +19709,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Fractional-Staff-Specialist-Endocrinology-VIC-3350/1362736566/</t>
+          <t>https://careers.grampianshealth.com/job/Stawell-Stawell-Consultant-Anaesthetist-VIC-3380/1363307366/</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -19117,7 +19723,7 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -19136,7 +19742,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -19148,17 +19754,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Medical Oncology Clinical Trials Fellow</t>
+          <t>Fractional Staff Specialist - Endocrinology</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fellow</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -19188,7 +19794,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Medical-Oncology-Clinical-Trials-Fellow-VIC-3350/1358341066/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Fractional-Staff-Specialist-Endocrinology-VIC-3350/1362736566/</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -19198,11 +19804,11 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Michael O'Brien</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -19216,29 +19822,34 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Transition Year - ICU</t>
+          <t>Medical Oncology Clinical Trials Fellow</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ICU</t>
+          <t>Oncology</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Fellow</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -19268,7 +19879,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Transition-Year-ICU-VIC-3350/1362867666/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Medical-Oncology-Clinical-Trials-Fellow-VIC-3350/1358341066/</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -19278,7 +19889,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="M81" t="n">
@@ -19301,7 +19912,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -19313,12 +19924,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Psychiatric Enrolled Nurse - Central Allocations Unit</t>
+          <t>Transition Year - ICU</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>ICU</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -19348,7 +19959,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Psychiatric-Enrolled-Nurse-Central-Allocations-Unit-VIC-3350/1332132666/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Transition-Year-ICU-VIC-3350/1362867666/</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -19381,7 +19992,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -19393,17 +20004,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2027 Fellow - General Surgery</t>
+          <t>Psychiatric Enrolled Nurse - Central Allocations Unit</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>General Surgery</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Fellow</t>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -19433,7 +20039,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-2027-Fellow-General-Surgery-VIC-3350/1363551666/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Psychiatric-Enrolled-Nurse-Central-Allocations-Unit-VIC-3350/1332132666/</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -19466,7 +20072,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -19478,12 +20084,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>International Job Seekers</t>
+          <t>2027 Fellow - General Surgery</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Fellow</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -19513,7 +20124,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>https://www.gh.org.au/careers-and-training/international-recruitment/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-2027-Fellow-General-Surgery-VIC-3350/1363551666/</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -19527,7 +20138,7 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -19546,7 +20157,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -19558,17 +20169,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Provisional Fellow - Anaesthetics</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Anaesthesia</t>
+          <t>International Job Seekers</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fellow</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -19598,7 +20204,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Provisional-Fellow-Anaesthetics-VIC-3350/1362205366/</t>
+          <t>https://www.gh.org.au/careers-and-training/international-recruitment/</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -19631,7 +20237,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -19643,22 +20249,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2027 Senior Registrar - Obstetrics &amp; Gynaecology</t>
+          <t>Provisional Fellow - Anaesthetics</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Obstetrics &amp; Gynaecology</t>
+          <t>Anaesthesia</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Senior Registrar</t>
+          <t>Fellow</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Eastern Health</t>
+          <t>Grampians Health</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -19683,21 +20289,21 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Senior-Registrar-Obstetrics-&amp;-Gynaecology-VIC-3128/1362270666/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Provisional-Fellow-Anaesthetics-VIC-3350/1362205366/</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Eastern_Health</t>
+          <t>Grampians_Health</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Dr. Priya Sharma</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -19709,22 +20315,31 @@
           <t>Primary — configured method</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+        </is>
+      </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2027 Emergency Medicine Registrar</t>
+          <t>Registrar - Psychiatry</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Emergency Medicine</t>
+          <t>Psychiatry</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -19734,7 +20349,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Eastern Health</t>
+          <t>Grampians Health</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -19747,33 +20362,34 @@
           <t>VIC</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>30-06-2026 21:27</t>
+          <t>02-07-2026 09:22</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Emergency-Medicine-Registrar-VIC-3128/1360650666/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Psychiatry-VIC-3350/1362426866/</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Eastern_Health</t>
+          <t>Grampians_Health</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -19787,29 +20403,35 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Weak title relevance; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>1 day old</t>
-        </is>
-      </c>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Weak title relevance; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026 Paediatric Registrar (August 2026)</t>
+          <t>2027 Senior Registrar - Obstetrics &amp; Gynaecology</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Obstetrics &amp; Gynaecology</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Senior Registrar</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -19839,7 +20461,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2026-Paediatric-Registrar-%28August-2026%29-VIC-3128/1357355466/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Senior-Registrar-Obstetrics-&amp;-Gynaecology-VIC-3128/1362270666/</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -19849,11 +20471,11 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Priya Sharma</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -19865,31 +20487,22 @@
           <t>Primary — configured method</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Weak title relevance; Specialty mismatch</t>
-        </is>
-      </c>
+      <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>1 day old</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>Weak title relevance; Specialty mismatch</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2027 ENT Registrar (Unaccredited)</t>
+          <t>2027 Emergency Medicine Registrar</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>Emergency Medicine</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -19924,7 +20537,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-ENT-Registrar-%28Unaccredited%29-VIC-3128/1362728766/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Emergency-Medicine-Registrar-VIC-3128/1360650666/</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -19934,11 +20547,11 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -19952,29 +20565,24 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch</t>
+          <t>Weak title relevance; Experience level mismatch</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch</t>
+          <t>Weak title relevance; Experience level mismatch</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2027 Urology Registrar (Unaccredited)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Urology</t>
+          <t>2026 Paediatric Registrar (August 2026)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -20009,7 +20617,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Urology-Registrar-%28Unaccredited%29-VIC-3128/1363055466/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2026-Paediatric-Registrar-%28August-2026%29-VIC-3128/1357355466/</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -20023,7 +20631,7 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -20042,7 +20650,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -20054,7 +20662,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2027 General Surgical Registrar (Un-Accredited)</t>
+          <t>2027 ENT Registrar (Unaccredited)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ENT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -20089,7 +20702,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-General-Surgical-Registrar-%28Un-Accredited%29-VIC-3128/1361833966/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-ENT-Registrar-%28Unaccredited%29-VIC-3128/1362728766/</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -20103,7 +20716,7 @@
         </is>
       </c>
       <c r="M91" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -20122,7 +20735,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -20134,12 +20747,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Addiction Psychiatry Registrar</t>
+          <t>2027 Urology Registrar (Unaccredited)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Psychiatry</t>
+          <t>Urology</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -20174,7 +20787,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Richmond-Addiction-Psychiatry-Registrar-VIC-3121/1362615666/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Urology-Registrar-%28Unaccredited%29-VIC-3128/1363055466/</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -20188,7 +20801,7 @@
         </is>
       </c>
       <c r="M92" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -20207,7 +20820,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -20219,7 +20832,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026 Addiction Medicine Registrar</t>
+          <t>2027 General Surgical Registrar (Un-Accredited)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -20254,7 +20867,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2026-Addiction-Medicine-Registrar-VIC-3128/1361029166/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-General-Surgical-Registrar-%28Un-Accredited%29-VIC-3128/1361833966/</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -20268,7 +20881,7 @@
         </is>
       </c>
       <c r="M93" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -20287,7 +20900,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -20299,7 +20912,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2027 Addiction Medicine Registrar</t>
+          <t>Addiction Psychiatry Registrar</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Psychiatry</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -20334,7 +20952,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Addiction-Medicine-Registrar-VIC-3128/1361030066/</t>
+          <t>https://careers.easternhealth.org.au/job/Richmond-Addiction-Psychiatry-Registrar-VIC-3121/1362615666/</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -20367,7 +20985,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -20379,7 +20997,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2027 Plastic Surgery Unaccredited Registrar</t>
+          <t>2026 Addiction Medicine Registrar</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -20414,7 +21032,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Plastic-Surgery-Unaccredited-Registrar-VIC-3128/1362416266/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2026-Addiction-Medicine-Registrar-VIC-3128/1361029166/</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -20428,7 +21046,7 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -20447,7 +21065,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -20459,12 +21077,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2027 Upper Gastro Intestinal Research Fellow</t>
+          <t>2027 Addiction Medicine Registrar</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fellow</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -20494,7 +21112,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Upper-Gastro-Intestinal-Research-Fellow-VIC-3128/1363489266/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Addiction-Medicine-Registrar-VIC-3128/1361030066/</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -20508,7 +21126,7 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -20522,39 +21140,34 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2027 Senior Registrar General Medicine</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Internal Medicine</t>
+          <t>2027 Plastic Surgery Unaccredited Registrar</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Senior Registrar</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Royal Children's Hospital</t>
+          <t>Eastern Health</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -20579,21 +21192,21 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Senior-Registrar-General-Medicine/1362878366/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Plastic-Surgery-Unaccredited-Registrar-VIC-3128/1362416266/</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>RCH</t>
+          <t>Eastern_Health</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -20607,34 +21220,34 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Weak title relevance; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Weak title relevance; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2027 Paediatric Registrars VPAT (Advanced and Continuing Trainees)</t>
+          <t>2027 Upper Gastro Intestinal Research Fellow</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Fellow</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Royal Children's Hospital</t>
+          <t>Eastern Health</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -20659,12 +21272,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Paediatric-Registrars-VPAT-%28Advanced-and-Continuing-Trainees%29/1361643566/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Upper-Gastro-Intestinal-Research-Fellow-VIC-3128/1363489266/</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>RCH</t>
+          <t>Eastern_Health</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -20673,7 +21286,7 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -20687,34 +21300,34 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch</t>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch</t>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2027 Immunopathology Registrar / Fellow</t>
+          <t>2027 Senior Registrar General Medicine</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pathology</t>
+          <t>Internal Medicine</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Senior Registrar</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -20744,7 +21357,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Immunopathology-Registrar-Fellow/1363389666/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Senior-Registrar-General-Medicine/1362878366/</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -20754,11 +21367,11 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Dr. Priya Sharma</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="M99" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -20772,29 +21385,24 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch</t>
+          <t>Weak title relevance; Experience level mismatch</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch</t>
+          <t>Weak title relevance; Experience level mismatch</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2027 RCH NICU - VPAT Registrar</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>ICU</t>
+          <t>2027 Paediatric Registrars VPAT (Advanced and Continuing Trainees)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -20829,7 +21437,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-RCH-NICU-VPAT-Registrar/1363270566/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Paediatric-Registrars-VPAT-%28Advanced-and-Continuing-Trainees%29/1361643566/</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -20843,7 +21451,7 @@
         </is>
       </c>
       <c r="M100" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -20862,7 +21470,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -20874,7 +21482,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Microbiology Registrar 2027</t>
+          <t>2027 Immunopathology Registrar / Fellow</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Pathology</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -20909,7 +21522,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Microbiology-Registrar-2027/1363255766/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Immunopathology-Registrar-Fellow/1363389666/</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -20919,11 +21532,11 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Priya Sharma</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -20942,7 +21555,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -20954,7 +21567,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2027 Allergy &amp; Immunology Fellow / Registrar</t>
+          <t>2027 RCH NICU - VPAT Registrar</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ICU</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -20989,7 +21607,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Allergy-&amp;-Immunology-Fellow-Registrar/1363326766/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-RCH-NICU-VPAT-Registrar/1363270566/</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -21003,7 +21621,7 @@
         </is>
       </c>
       <c r="M102" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -21022,7 +21640,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -21034,17 +21652,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Neurology Consultant</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Neurology</t>
+          <t>Microbiology Registrar 2027</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -21074,7 +21687,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Neurology-Consultant/1362944566/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Microbiology-Registrar-2027/1363255766/</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -21084,11 +21697,11 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Dr. Michael O'Brien</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="M103" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -21107,7 +21720,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -21119,12 +21732,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2027 Unaccredited Ophthalmology Registrar</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Ophthalmology</t>
+          <t>2027 Allergy &amp; Immunology Fellow / Registrar</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -21147,20 +21755,19 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>01-07-2026 09:20</t>
+          <t>30-06-2026 21:27</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Unaccredited-Ophthalmology-Registrar/1357689666/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Allergy-&amp;-Immunology-Fellow-Registrar/1363326766/</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -21174,7 +21781,7 @@
         </is>
       </c>
       <c r="M104" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -21193,10 +21800,9 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr"/>
+          <t>2 days old</t>
+        </is>
+      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -21206,32 +21812,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Paediatrics &amp; Child Health</t>
+          <t>Neurology Consultant</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Internal Medicine</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Fellow</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>RACP Member Hospital (AU)</t>
+          <t>Royal Children's Hospital</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>nt</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -21246,21 +21852,21 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/basic-training/paediatrics-child-health</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Neurology-Consultant/1362944566/</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>RACP</t>
+          <t>RCH</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Michael O'Brien</t>
         </is>
       </c>
       <c r="M105" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -21274,78 +21880,78 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Weak title relevance; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>Weak title relevance; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Adult Internal Medicine</t>
+          <t>2027 Unaccredited Ophthalmology Registrar</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Internal Medicine</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Fellow</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>RACP Member Hospital (AU)</t>
+          <t>Royal Children's Hospital</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>nt</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>30-06-2026 21:27</t>
+          <t>01-07-2026 09:20</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/basic-training/adult-internal-medicine</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Unaccredited-Ophthalmology-Registrar/1357689666/</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>RACP</t>
+          <t>RCH</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="M106" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -21359,7 +21965,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Weak title relevance; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -21369,14 +21975,14 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Weak title relevance; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Adolescent and Young Adult Medicine</t>
+          <t>Paediatrics &amp; Child Health</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -21416,7 +22022,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/adolescent-and-young-adult-medicine</t>
+          <t>https://www.racp.edu.au/trainees/basic-training/paediatrics-child-health</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -21430,7 +22036,7 @@
         </is>
       </c>
       <c r="M107" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
@@ -21449,7 +22055,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -21461,7 +22067,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Addiction Medicine</t>
+          <t>Adult Internal Medicine</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -21501,7 +22107,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/addiction-medicine</t>
+          <t>https://www.racp.edu.au/trainees/basic-training/adult-internal-medicine</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -21515,7 +22121,7 @@
         </is>
       </c>
       <c r="M108" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -21534,7 +22140,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -21546,7 +22152,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>New curricula</t>
+          <t>Adolescent and Young Adult Medicine</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -21586,7 +22192,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/new-curricula</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/adolescent-and-young-adult-medicine</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -21600,7 +22206,7 @@
         </is>
       </c>
       <c r="M109" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -21619,7 +22225,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -21631,7 +22237,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Advanced Training - New Curricula</t>
+          <t>Addiction Medicine</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -21671,7 +22277,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/recognition-of-prior-learning/advanced-training-new-curricula</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/addiction-medicine</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -21685,7 +22291,7 @@
         </is>
       </c>
       <c r="M110" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -21704,7 +22310,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -21716,7 +22322,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>New curricula</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -21756,7 +22362,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/cardiology</t>
+          <t>https://www.racp.edu.au/trainees/new-curricula</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -21770,7 +22376,7 @@
         </is>
       </c>
       <c r="M111" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -21789,7 +22395,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -21801,7 +22407,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Post-Fellowship training</t>
+          <t>Advanced Training - New Curricula</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -21841,7 +22447,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/multi-specialty-training-options/post-fellowship-training</t>
+          <t>https://www.racp.edu.au/trainees/recognition-of-prior-learning/advanced-training-new-curricula</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -21855,7 +22461,7 @@
         </is>
       </c>
       <c r="M112" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -21874,7 +22480,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -21886,7 +22492,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Prizes, grants, scholarships and fellowships</t>
+          <t>Cardiology</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Internal Medicine</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -21921,7 +22532,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/become-a-physician/prizes-grants-scholarships-and-fellowships</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/cardiology</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -21935,7 +22546,7 @@
         </is>
       </c>
       <c r="M113" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -21949,29 +22560,34 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+          <t>Weak title relevance; Experience level mismatch</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+          <t>Weak title relevance; Experience level mismatch</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>The President's Message</t>
+          <t>Post-Fellowship training</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ENT</t>
+          <t>Internal Medicine</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Fellow</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -21986,7 +22602,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -22001,7 +22617,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/news-and-events/presidents-message</t>
+          <t>https://www.racp.edu.au/trainees/multi-specialty-training-options/post-fellowship-training</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -22015,7 +22631,7 @@
         </is>
       </c>
       <c r="M114" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
@@ -22029,29 +22645,24 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+          <t>Weak title relevance; Experience level mismatch</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+          <t>Weak title relevance; Experience level mismatch</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Supervisor Professional Development Program</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>ENT</t>
+          <t>Prizes, grants, scholarships and fellowships</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -22071,7 +22682,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -22086,7 +22697,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/supervision/supervisor-professional-development-program</t>
+          <t>https://www.racp.edu.au/become-a-physician/prizes-grants-scholarships-and-fellowships</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -22096,11 +22707,11 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="M115" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
@@ -22119,7 +22730,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -22131,7 +22742,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Represent your Profession</t>
+          <t>The President's Message</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -22166,7 +22777,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/policy-and-advocacy/represent-your-profession</t>
+          <t>https://www.racp.edu.au/news-and-events/presidents-message</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -22199,7 +22810,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -22211,7 +22822,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Continuing Professional Development</t>
+          <t>Supervisor Professional Development Program</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -22251,7 +22862,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/continuing-professional-development</t>
+          <t>https://www.racp.edu.au/fellows/supervision/supervisor-professional-development-program</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -22265,7 +22876,7 @@
         </is>
       </c>
       <c r="M117" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N117" t="inlineStr">
         <is>
@@ -22284,7 +22895,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -22296,7 +22907,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CPD Recognition and Assessment Framework</t>
+          <t>Represent your Profession</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -22304,11 +22915,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Fellow</t>
-        </is>
-      </c>
       <c r="D118" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -22336,7 +22942,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework</t>
+          <t>https://www.racp.edu.au/policy-and-advocacy/represent-your-profession</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -22346,11 +22952,11 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="M118" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -22369,7 +22975,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -22381,7 +22987,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CAPE Program-Level Requirements</t>
+          <t>Continuing Professional Development</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -22421,7 +23027,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework/cape-program-level-requirements</t>
+          <t>https://www.racp.edu.au/fellows/continuing-professional-development</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -22431,7 +23037,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="M119" t="n">
@@ -22454,7 +23060,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -22466,7 +23072,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Prevocational Training and Entry to Basic Training</t>
+          <t>CPD Recognition and Assessment Framework</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -22474,6 +23080,11 @@
           <t>ENT</t>
         </is>
       </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Fellow</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -22501,7 +23112,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/become-a-physician/entry-into-basic-training/prevocational-training-and-entry-to-basic-training</t>
+          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -22511,11 +23122,11 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="M120" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -22534,7 +23145,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -22546,7 +23157,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Position design and posting</t>
+          <t>CAPE Program-Level Requirements</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -22586,7 +23197,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/local-selection/position-design-and-posting</t>
+          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework/cape-program-level-requirements</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -22600,7 +23211,7 @@
         </is>
       </c>
       <c r="M121" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -22619,7 +23230,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -22631,7 +23242,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Student Scholarships &amp; Prizes</t>
+          <t>Prevocational Training and Entry to Basic Training</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -22666,7 +23277,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/foundation/student-scholarships-and-prizes</t>
+          <t>https://www.racp.edu.au/become-a-physician/entry-into-basic-training/prevocational-training-and-entry-to-basic-training</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -22676,11 +23287,11 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="M122" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
@@ -22699,7 +23310,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -22711,7 +23322,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Selection into Training Quality Assurance and Improvement</t>
+          <t>Position design and posting</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -22719,6 +23330,11 @@
           <t>ENT</t>
         </is>
       </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Fellow</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -22746,7 +23362,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/become-a-physician/selection-into-training-quality-assurance-and-improvement</t>
+          <t>https://www.racp.edu.au/fellows/local-selection/position-design-and-posting</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -22756,11 +23372,11 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="M123" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
@@ -22779,7 +23395,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -22791,7 +23407,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Becoming a Fellow</t>
+          <t>Student Scholarships &amp; Prizes</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -22799,11 +23415,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Fellow</t>
-        </is>
-      </c>
       <c r="D124" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -22831,7 +23442,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/becoming-a-fellow</t>
+          <t>https://www.racp.edu.au/foundation/student-scholarships-and-prizes</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -22841,7 +23452,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="M124" t="n">
@@ -22864,7 +23475,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -22876,12 +23487,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>International Grants</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Intern</t>
+          <t>Selection into Training Quality Assurance and Improvement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ENT</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -22911,7 +23522,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/foundation/international-grants</t>
+          <t>https://www.racp.edu.au/become-a-physician/selection-into-training-quality-assurance-and-improvement</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -22921,11 +23532,11 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="M125" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
@@ -22944,7 +23555,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -22956,7 +23567,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Our recipients</t>
+          <t>Becoming a Fellow</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -22964,6 +23575,11 @@
           <t>ENT</t>
         </is>
       </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Fellow</t>
+        </is>
+      </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -22991,7 +23607,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/foundation/our-recipients</t>
+          <t>https://www.racp.edu.au/fellows/becoming-a-fellow</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -23005,7 +23621,7 @@
         </is>
       </c>
       <c r="M126" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
@@ -23024,7 +23640,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -23036,12 +23652,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>News &amp; Events</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>ENT</t>
+          <t>International Grants</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -23071,7 +23687,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/news-and-events</t>
+          <t>https://www.racp.edu.au/foundation/international-grants</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -23081,11 +23697,11 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="M127" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -23104,7 +23720,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -23116,83 +23732,243 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>Our recipients</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>RACP Member Hospital (AU)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>nt</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>30-06-2026 21:27</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>https://www.racp.edu.au/foundation/our-recipients</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>RACP</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Dr. James Chen</t>
+        </is>
+      </c>
+      <c r="M128" t="n">
+        <v>13</v>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Primary — configured method</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>2 days old</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>News &amp; Events</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>RACP Member Hospital (AU)</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>nt</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>30-06-2026 21:27</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>https://www.racp.edu.au/news-and-events</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>RACP</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Dr. Sarah Williams</t>
+        </is>
+      </c>
+      <c r="M129" t="n">
+        <v>12</v>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Primary — configured method</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>2 days old</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
           <t>New Fellow Survey</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>ENT</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Fellow</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>nt</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>NT</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>30-06-2026</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="I130" t="inlineStr">
         <is>
           <t>30-06-2026 21:27</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
+      <c r="J130" t="inlineStr">
         <is>
           <t>https://www.racp.edu.au/fellows/becoming-a-fellow/new-fellow-survey</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="K130" t="inlineStr">
         <is>
           <t>RACP</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t>Dr. James Chen</t>
         </is>
       </c>
-      <c r="M128" t="n">
+      <c r="M130" t="n">
         <v>12</v>
       </c>
-      <c r="N128" t="inlineStr">
+      <c r="N130" t="inlineStr">
         <is>
           <t>static_html</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr">
+      <c r="O130" t="inlineStr">
         <is>
           <t>Primary — configured method</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr">
+      <c r="P130" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
         </is>
       </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>1 day old</t>
-        </is>
-      </c>
-      <c r="S128" t="inlineStr">
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>2 days old</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
         </is>
@@ -23209,7 +23985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -26741,27 +27517,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2027 O&amp;G Senior Registrar</t>
+          <t>Fellow - Trauma Surgery</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The_Womens</t>
+          <t>WA_Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>The Royal Women's Hospital</t>
+          <t>WA Health</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://careers.thewomens.org.au/job/2027-O&amp;amp;G-Senior-Registrar/2053-en_GB</t>
+          <t>https://medcareerswa.health.wa.gov.au/jobs/fellow-trauma-surgery-royal-perth-hospital-wa-australia-62611f69-14e4-407c-8c70-27588eb003f2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -26770,38 +27546,38 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="H71" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I71" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J71" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="K71" t="n">
         <v>12</v>
       </c>
       <c r="L71" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Obstetrics &amp; Gynaecology Registrar (Accredited)</t>
+          <t>2027 O&amp;G Senior Registrar</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Grampians_Health</t>
+          <t>The_Womens</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Grampians Health</t>
+          <t>The Royal Women's Hospital</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -26811,7 +27587,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Obstetrics-&amp;-Gynaecology-Registrar-%28Accredited%29-VIC-3350/1362508966/</t>
+          <t>https://careers.thewomens.org.au/job/2027-O&amp;amp;G-Senior-Registrar/2053-en_GB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -26820,28 +27596,28 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H72" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J72" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K72" t="n">
         <v>12</v>
       </c>
       <c r="L72" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Registrar - Obstetrics &amp; Gynaecology Unaccredited</t>
+          <t>Obstetrics &amp; Gynaecology Registrar (Accredited)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -26861,7 +27637,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Obstetrics-&amp;-Gynaecology-Unaccredited-VIC-3350/1357598066/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Obstetrics-&amp;-Gynaecology-Registrar-%28Accredited%29-VIC-3350/1362508966/</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -26870,28 +27646,28 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H73" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I73" t="n">
+        <v>16</v>
+      </c>
+      <c r="J73" t="n">
+        <v>39</v>
+      </c>
+      <c r="K73" t="n">
         <v>12</v>
       </c>
-      <c r="J73" t="n">
-        <v>40</v>
-      </c>
-      <c r="K73" t="n">
-        <v>10</v>
-      </c>
       <c r="L73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Registrar - General Medicine Advanced Trainee</t>
+          <t>Registrar - Obstetrics &amp; Gynaecology Unaccredited</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -26911,37 +27687,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-General-Medicine-Advanced-Trainee-VIC-3350/1362283766/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Obstetrics-&amp;-Gynaecology-Unaccredited-VIC-3350/1357598066/</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dr. Michael O'Brien</t>
+          <t>Dr. Priya Sharma</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="H74" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="I74" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="J74" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K74" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="L74" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Registrar - Surgical Plastics (Unaccredited)</t>
+          <t>Registrar - General Medicine Advanced Trainee</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -26961,37 +27737,37 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Surgical-Plastics-%28Unaccredited%29-VIC-3350/1362050466/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-General-Medicine-Advanced-Trainee-VIC-3350/1362283766/</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Michael O'Brien</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H75" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I75" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J75" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K75" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="L75" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2027 General Surgery Registrar -Unaccredited</t>
+          <t>Registrar - Surgical Plastics (Unaccredited)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -27011,7 +27787,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-2027-General-Surgery-Registrar-Unaccredited-VIC-3350/1362049866/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Surgical-Plastics-%28Unaccredited%29-VIC-3350/1362050466/</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -27020,28 +27796,28 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H76" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J76" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K76" t="n">
+        <v>10</v>
+      </c>
+      <c r="L76" t="n">
         <v>15</v>
-      </c>
-      <c r="L76" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Registrar - Urology Unaccredited</t>
+          <t>2027 General Surgery Registrar -Unaccredited</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -27061,7 +27837,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Urology-Unaccredited-VIC-3350/1362036766/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-2027-General-Surgery-Registrar-Unaccredited-VIC-3350/1362049866/</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -27070,28 +27846,28 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H77" t="n">
         <v>35</v>
       </c>
       <c r="I77" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L77" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Stawell - Consultant Anaesthetist</t>
+          <t>Registrar - Urology Unaccredited</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -27111,37 +27887,37 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Stawell-Stawell-Consultant-Anaesthetist-VIC-3380/1363307366/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Urology-Unaccredited-VIC-3350/1362036766/</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dr. Michael O'Brien</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="G78" t="n">
+        <v>36</v>
+      </c>
+      <c r="H78" t="n">
         <v>35</v>
       </c>
-      <c r="H78" t="n">
-        <v>15</v>
-      </c>
       <c r="I78" t="n">
+        <v>13</v>
+      </c>
+      <c r="J78" t="n">
+        <v>36</v>
+      </c>
+      <c r="K78" t="n">
+        <v>10</v>
+      </c>
+      <c r="L78" t="n">
         <v>12</v>
-      </c>
-      <c r="J78" t="n">
-        <v>14</v>
-      </c>
-      <c r="K78" t="n">
-        <v>35</v>
-      </c>
-      <c r="L78" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Fractional Staff Specialist - Endocrinology</t>
+          <t>Stawell - Consultant Anaesthetist</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -27161,7 +27937,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Fractional-Staff-Specialist-Endocrinology-VIC-3350/1362736566/</t>
+          <t>https://careers.grampianshealth.com/job/Stawell-Stawell-Consultant-Anaesthetist-VIC-3380/1363307366/</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -27170,28 +27946,28 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H79" t="n">
+        <v>15</v>
+      </c>
+      <c r="I79" t="n">
+        <v>12</v>
+      </c>
+      <c r="J79" t="n">
+        <v>14</v>
+      </c>
+      <c r="K79" t="n">
+        <v>35</v>
+      </c>
+      <c r="L79" t="n">
         <v>13</v>
-      </c>
-      <c r="I79" t="n">
-        <v>16</v>
-      </c>
-      <c r="J79" t="n">
-        <v>18</v>
-      </c>
-      <c r="K79" t="n">
-        <v>34</v>
-      </c>
-      <c r="L79" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Medical Oncology Clinical Trials Fellow</t>
+          <t>Fractional Staff Specialist - Endocrinology</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -27211,37 +27987,37 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Medical-Oncology-Clinical-Trials-Fellow-VIC-3350/1358341066/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Fractional-Staff-Specialist-Endocrinology-VIC-3350/1362736566/</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Michael O'Brien</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H80" t="n">
         <v>13</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K80" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L80" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Transition Year - ICU</t>
+          <t>Medical Oncology Clinical Trials Fellow</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -27261,12 +28037,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Transition-Year-ICU-VIC-3350/1362867666/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Medical-Oncology-Clinical-Trials-Fellow-VIC-3350/1358341066/</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -27276,13 +28052,13 @@
         <v>13</v>
       </c>
       <c r="I81" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K81" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L81" t="n">
         <v>13</v>
@@ -27291,7 +28067,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Psychiatric Enrolled Nurse - Central Allocations Unit</t>
+          <t>Transition Year - ICU</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -27311,7 +28087,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Psychiatric-Enrolled-Nurse-Central-Allocations-Unit-VIC-3350/1332132666/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Transition-Year-ICU-VIC-3350/1362867666/</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -27323,7 +28099,7 @@
         <v>19</v>
       </c>
       <c r="H82" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I82" t="n">
         <v>15</v>
@@ -27341,7 +28117,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2027 Fellow - General Surgery</t>
+          <t>Psychiatric Enrolled Nurse - Central Allocations Unit</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -27361,7 +28137,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-2027-Fellow-General-Surgery-VIC-3350/1363551666/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Psychiatric-Enrolled-Nurse-Central-Allocations-Unit-VIC-3350/1332132666/</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -27373,7 +28149,7 @@
         <v>19</v>
       </c>
       <c r="H83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I83" t="n">
         <v>15</v>
@@ -27382,16 +28158,16 @@
         <v>19</v>
       </c>
       <c r="K83" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L83" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>International Job Seekers</t>
+          <t>2027 Fellow - General Surgery</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -27411,7 +28187,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://www.gh.org.au/careers-and-training/international-recruitment/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-2027-Fellow-General-Surgery-VIC-3350/1363551666/</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -27420,28 +28196,28 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H84" t="n">
+        <v>15</v>
+      </c>
+      <c r="I84" t="n">
+        <v>15</v>
+      </c>
+      <c r="J84" t="n">
+        <v>19</v>
+      </c>
+      <c r="K84" t="n">
         <v>16</v>
       </c>
-      <c r="I84" t="n">
-        <v>14</v>
-      </c>
-      <c r="J84" t="n">
-        <v>18</v>
-      </c>
-      <c r="K84" t="n">
-        <v>14</v>
-      </c>
       <c r="L84" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Provisional Fellow - Anaesthetics</t>
+          <t>International Job Seekers</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -27461,7 +28237,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Provisional-Fellow-Anaesthetics-VIC-3350/1362205366/</t>
+          <t>https://www.gh.org.au/careers-and-training/international-recruitment/</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -27473,35 +28249,35 @@
         <v>18</v>
       </c>
       <c r="H85" t="n">
+        <v>16</v>
+      </c>
+      <c r="I85" t="n">
         <v>14</v>
-      </c>
-      <c r="I85" t="n">
-        <v>13</v>
       </c>
       <c r="J85" t="n">
         <v>18</v>
       </c>
       <c r="K85" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L85" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2027 Senior Registrar - Obstetrics &amp; Gynaecology</t>
+          <t>Provisional Fellow - Anaesthetics</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Eastern_Health</t>
+          <t>Grampians_Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Eastern Health</t>
+          <t>Grampians Health</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -27511,47 +28287,47 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Senior-Registrar-Obstetrics-&amp;-Gynaecology-VIC-3128/1362270666/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Provisional-Fellow-Anaesthetics-VIC-3350/1362205366/</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dr. Priya Sharma</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="H86" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J86" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L86" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2027 Emergency Medicine Registrar</t>
+          <t>Registrar - Psychiatry</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Eastern_Health</t>
+          <t>Grampians_Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Eastern Health</t>
+          <t>Grampians Health</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -27561,37 +28337,37 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Emergency-Medicine-Registrar-VIC-3128/1360650666/</t>
+          <t>https://careers.grampianshealth.com/job/Ballarat-Central-Registrar-Psychiatry-VIC-3350/1362426866/</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H87" t="n">
         <v>31</v>
       </c>
       <c r="I87" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="J87" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K87" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="L87" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026 Paediatric Registrar (August 2026)</t>
+          <t>2027 Senior Registrar - Obstetrics &amp; Gynaecology</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -27611,37 +28387,37 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2026-Paediatric-Registrar-%28August-2026%29-VIC-3128/1357355466/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Senior-Registrar-Obstetrics-&amp;-Gynaecology-VIC-3128/1362270666/</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Priya Sharma</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="H88" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="I88" t="n">
+        <v>16</v>
+      </c>
+      <c r="J88" t="n">
+        <v>38</v>
+      </c>
+      <c r="K88" t="n">
+        <v>10</v>
+      </c>
+      <c r="L88" t="n">
         <v>15</v>
-      </c>
-      <c r="J88" t="n">
-        <v>41</v>
-      </c>
-      <c r="K88" t="n">
-        <v>14</v>
-      </c>
-      <c r="L88" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2027 ENT Registrar (Unaccredited)</t>
+          <t>2027 Emergency Medicine Registrar</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -27661,37 +28437,37 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-ENT-Registrar-%28Unaccredited%29-VIC-3128/1362728766/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Emergency-Medicine-Registrar-VIC-3128/1360650666/</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="G89" t="n">
+        <v>44</v>
+      </c>
+      <c r="H89" t="n">
+        <v>31</v>
+      </c>
+      <c r="I89" t="n">
+        <v>44</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34</v>
+      </c>
+      <c r="K89" t="n">
         <v>38</v>
       </c>
-      <c r="H89" t="n">
-        <v>33</v>
-      </c>
-      <c r="I89" t="n">
-        <v>13</v>
-      </c>
-      <c r="J89" t="n">
-        <v>38</v>
-      </c>
-      <c r="K89" t="n">
-        <v>12</v>
-      </c>
       <c r="L89" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2027 Urology Registrar (Unaccredited)</t>
+          <t>2026 Paediatric Registrar (August 2026)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -27711,7 +28487,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Urology-Registrar-%28Unaccredited%29-VIC-3128/1363055466/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2026-Paediatric-Registrar-%28August-2026%29-VIC-3128/1357355466/</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -27720,28 +28496,28 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H90" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I90" t="n">
         <v>15</v>
       </c>
       <c r="J90" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K90" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L90" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2027 General Surgical Registrar (Un-Accredited)</t>
+          <t>2027 ENT Registrar (Unaccredited)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -27761,7 +28537,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-General-Surgical-Registrar-%28Un-Accredited%29-VIC-3128/1361833966/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-ENT-Registrar-%28Unaccredited%29-VIC-3128/1362728766/</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -27770,28 +28546,28 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H91" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I91" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J91" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K91" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L91" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Addiction Psychiatry Registrar</t>
+          <t>2027 Urology Registrar (Unaccredited)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -27811,7 +28587,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Richmond-Addiction-Psychiatry-Registrar-VIC-3121/1362615666/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Urology-Registrar-%28Unaccredited%29-VIC-3128/1363055466/</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -27820,28 +28596,28 @@
         </is>
       </c>
       <c r="G92" t="n">
+        <v>37</v>
+      </c>
+      <c r="H92" t="n">
         <v>35</v>
-      </c>
-      <c r="H92" t="n">
-        <v>30</v>
       </c>
       <c r="I92" t="n">
         <v>15</v>
       </c>
       <c r="J92" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K92" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L92" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026 Addiction Medicine Registrar</t>
+          <t>2027 General Surgical Registrar (Un-Accredited)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -27861,7 +28637,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2026-Addiction-Medicine-Registrar-VIC-3128/1361029166/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-General-Surgical-Registrar-%28Un-Accredited%29-VIC-3128/1361833966/</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -27870,28 +28646,28 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H93" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I93" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J93" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K93" t="n">
         <v>15</v>
       </c>
       <c r="L93" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2027 Addiction Medicine Registrar</t>
+          <t>Addiction Psychiatry Registrar</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -27911,7 +28687,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Addiction-Medicine-Registrar-VIC-3128/1361030066/</t>
+          <t>https://careers.easternhealth.org.au/job/Richmond-Addiction-Psychiatry-Registrar-VIC-3121/1362615666/</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -27923,25 +28699,25 @@
         <v>35</v>
       </c>
       <c r="H94" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I94" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J94" t="n">
         <v>35</v>
       </c>
       <c r="K94" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L94" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2027 Plastic Surgery Unaccredited Registrar</t>
+          <t>2026 Addiction Medicine Registrar</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -27961,7 +28737,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Plastic-Surgery-Unaccredited-Registrar-VIC-3128/1362416266/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2026-Addiction-Medicine-Registrar-VIC-3128/1361029166/</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -27970,28 +28746,28 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H95" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I95" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J95" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K95" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L95" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2027 Upper Gastro Intestinal Research Fellow</t>
+          <t>2027 Addiction Medicine Registrar</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -28011,7 +28787,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Upper-Gastro-Intestinal-Research-Fellow-VIC-3128/1363489266/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Addiction-Medicine-Registrar-VIC-3128/1361030066/</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -28020,38 +28796,38 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H96" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I96" t="n">
         <v>16</v>
       </c>
       <c r="J96" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="K96" t="n">
+        <v>15</v>
+      </c>
+      <c r="L96" t="n">
         <v>16</v>
-      </c>
-      <c r="L96" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2027 Senior Registrar General Medicine</t>
+          <t>2027 Plastic Surgery Unaccredited Registrar</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RCH</t>
+          <t>Eastern_Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Royal Children's Hospital</t>
+          <t>Eastern Health</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -28061,47 +28837,47 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Senior-Registrar-General-Medicine/1362878366/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Plastic-Surgery-Unaccredited-Registrar-VIC-3128/1362416266/</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H97" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I97" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="J97" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K97" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="L97" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2027 Paediatric Registrars VPAT (Advanced and Continuing Trainees)</t>
+          <t>2027 Upper Gastro Intestinal Research Fellow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>RCH</t>
+          <t>Eastern_Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Royal Children's Hospital</t>
+          <t>Eastern Health</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -28111,7 +28887,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Paediatric-Registrars-VPAT-%28Advanced-and-Continuing-Trainees%29/1361643566/</t>
+          <t>https://careers.easternhealth.org.au/job/Eastern-Health-2027-Upper-Gastro-Intestinal-Research-Fellow-VIC-3128/1363489266/</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -28120,28 +28896,28 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H98" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="I98" t="n">
         <v>16</v>
       </c>
       <c r="J98" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K98" t="n">
         <v>16</v>
       </c>
       <c r="L98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2027 Immunopathology Registrar / Fellow</t>
+          <t>2027 Senior Registrar General Medicine</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -28161,37 +28937,37 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Immunopathology-Registrar-Fellow/1363389666/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Senior-Registrar-General-Medicine/1362878366/</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dr. Priya Sharma</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H99" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I99" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="J99" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K99" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="L99" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2027 RCH NICU - VPAT Registrar</t>
+          <t>2027 Paediatric Registrars VPAT (Advanced and Continuing Trainees)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -28211,7 +28987,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-RCH-NICU-VPAT-Registrar/1363270566/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Paediatric-Registrars-VPAT-%28Advanced-and-Continuing-Trainees%29/1361643566/</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -28220,28 +28996,28 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H100" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I100" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J100" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K100" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L100" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Microbiology Registrar 2027</t>
+          <t>2027 Immunopathology Registrar / Fellow</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -28261,28 +29037,28 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Microbiology-Registrar-2027/1363255766/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Immunopathology-Registrar-Fellow/1363389666/</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Priya Sharma</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H101" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I101" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J101" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K101" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L101" t="n">
         <v>14</v>
@@ -28291,7 +29067,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2027 Allergy &amp; Immunology Fellow / Registrar</t>
+          <t>2027 RCH NICU - VPAT Registrar</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -28311,7 +29087,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Allergy-&amp;-Immunology-Fellow-Registrar/1363326766/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-RCH-NICU-VPAT-Registrar/1363270566/</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -28320,28 +29096,28 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H102" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I102" t="n">
+        <v>12</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34</v>
+      </c>
+      <c r="K102" t="n">
+        <v>13</v>
+      </c>
+      <c r="L102" t="n">
         <v>15</v>
-      </c>
-      <c r="J102" t="n">
-        <v>33</v>
-      </c>
-      <c r="K102" t="n">
-        <v>14</v>
-      </c>
-      <c r="L102" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Neurology Consultant</t>
+          <t>Microbiology Registrar 2027</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -28361,37 +29137,37 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Neurology-Consultant/1362944566/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Microbiology-Registrar-2027/1363255766/</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dr. Michael O'Brien</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H103" t="n">
+        <v>33</v>
+      </c>
+      <c r="I103" t="n">
         <v>15</v>
       </c>
-      <c r="I103" t="n">
+      <c r="J103" t="n">
+        <v>34</v>
+      </c>
+      <c r="K103" t="n">
+        <v>13</v>
+      </c>
+      <c r="L103" t="n">
         <v>14</v>
-      </c>
-      <c r="J103" t="n">
-        <v>14</v>
-      </c>
-      <c r="K103" t="n">
-        <v>31</v>
-      </c>
-      <c r="L103" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2027 Unaccredited Ophthalmology Registrar</t>
+          <t>2027 Allergy &amp; Immunology Fellow / Registrar</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -28411,7 +29187,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Unaccredited-Ophthalmology-Registrar/1357689666/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Allergy-&amp;-Immunology-Fellow-Registrar/1363326766/</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -28420,128 +29196,128 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H104" t="n">
         <v>32</v>
       </c>
       <c r="I104" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J104" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K104" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L104" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Paediatrics &amp; Child Health</t>
+          <t>Neurology Consultant</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RACP</t>
+          <t>RCH</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>RACP Member Hospital (AU)</t>
+          <t>Royal Children's Hospital</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/basic-training/paediatrics-child-health</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Neurology-Consultant/1362944566/</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Michael O'Brien</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H105" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I105" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="J105" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="K105" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L105" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Adult Internal Medicine</t>
+          <t>2027 Unaccredited Ophthalmology Registrar</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RACP</t>
+          <t>RCH</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>RACP Member Hospital (AU)</t>
+          <t>Royal Children's Hospital</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/basic-training/adult-internal-medicine</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Unaccredited-Ophthalmology-Registrar/1357689666/</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H106" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="I106" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="J106" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K106" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="L106" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Adolescent and Young Adult Medicine</t>
+          <t>Paediatrics &amp; Child Health</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -28561,7 +29337,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/adolescent-and-young-adult-medicine</t>
+          <t>https://www.racp.edu.au/trainees/basic-training/paediatrics-child-health</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -28570,28 +29346,28 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H107" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I107" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J107" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="K107" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L107" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Addiction Medicine</t>
+          <t>Adult Internal Medicine</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -28611,7 +29387,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/addiction-medicine</t>
+          <t>https://www.racp.edu.au/trainees/basic-training/adult-internal-medicine</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -28620,28 +29396,28 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H108" t="n">
         <v>9</v>
       </c>
       <c r="I108" t="n">
+        <v>42</v>
+      </c>
+      <c r="J108" t="n">
+        <v>12</v>
+      </c>
+      <c r="K108" t="n">
         <v>41</v>
       </c>
-      <c r="J108" t="n">
-        <v>11</v>
-      </c>
-      <c r="K108" t="n">
-        <v>34</v>
-      </c>
       <c r="L108" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>New curricula</t>
+          <t>Adolescent and Young Adult Medicine</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -28661,7 +29437,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/new-curricula</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/adolescent-and-young-adult-medicine</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -28670,19 +29446,19 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H109" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I109" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J109" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K109" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L109" t="n">
         <v>35</v>
@@ -28691,7 +29467,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Advanced Training - New Curricula</t>
+          <t>Addiction Medicine</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -28711,7 +29487,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/recognition-of-prior-learning/advanced-training-new-curricula</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/addiction-medicine</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -28720,28 +29496,28 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H110" t="n">
         <v>9</v>
       </c>
       <c r="I110" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J110" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K110" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L110" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>New curricula</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -28761,7 +29537,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/cardiology</t>
+          <t>https://www.racp.edu.au/trainees/new-curricula</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -28770,28 +29546,28 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H111" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I111" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J111" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K111" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L111" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Post-Fellowship training</t>
+          <t>Advanced Training - New Curricula</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -28811,7 +29587,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/multi-specialty-training-options/post-fellowship-training</t>
+          <t>https://www.racp.edu.au/trainees/recognition-of-prior-learning/advanced-training-new-curricula</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -28820,19 +29596,19 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H112" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I112" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J112" t="n">
         <v>8</v>
       </c>
       <c r="K112" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L112" t="n">
         <v>35</v>
@@ -28841,7 +29617,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Prizes, grants, scholarships and fellowships</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -28861,7 +29637,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/become-a-physician/prizes-grants-scholarships-and-fellowships</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/cardiology</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -28870,28 +29646,28 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="H113" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I113" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J113" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K113" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="L113" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>The President's Message</t>
+          <t>Post-Fellowship training</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -28906,12 +29682,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/news-and-events/presidents-message</t>
+          <t>https://www.racp.edu.au/trainees/multi-specialty-training-options/post-fellowship-training</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -28920,28 +29696,28 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H114" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I114" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="J114" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K114" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="L114" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Supervisor Professional Development Program</t>
+          <t>Prizes, grants, scholarships and fellowships</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -28956,42 +29732,42 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/supervision/supervisor-professional-development-program</t>
+          <t>https://www.racp.edu.au/become-a-physician/prizes-grants-scholarships-and-fellowships</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H115" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I115" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J115" t="n">
         <v>9</v>
       </c>
       <c r="K115" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L115" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Represent your Profession</t>
+          <t>The President's Message</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -29011,7 +29787,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/policy-and-advocacy/represent-your-profession</t>
+          <t>https://www.racp.edu.au/news-and-events/presidents-message</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -29023,7 +29799,7 @@
         <v>17</v>
       </c>
       <c r="H116" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I116" t="n">
         <v>17</v>
@@ -29032,16 +29808,16 @@
         <v>10</v>
       </c>
       <c r="K116" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L116" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Continuing Professional Development</t>
+          <t>Supervisor Professional Development Program</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -29061,7 +29837,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/continuing-professional-development</t>
+          <t>https://www.racp.edu.au/fellows/supervision/supervisor-professional-development-program</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -29070,28 +29846,28 @@
         </is>
       </c>
       <c r="G117" t="n">
+        <v>17</v>
+      </c>
+      <c r="H117" t="n">
+        <v>9</v>
+      </c>
+      <c r="I117" t="n">
         <v>16</v>
-      </c>
-      <c r="H117" t="n">
-        <v>6</v>
-      </c>
-      <c r="I117" t="n">
-        <v>14</v>
       </c>
       <c r="J117" t="n">
         <v>9</v>
       </c>
       <c r="K117" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L117" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CPD Recognition and Assessment Framework</t>
+          <t>Represent your Profession</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -29111,37 +29887,37 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework</t>
+          <t>https://www.racp.edu.au/policy-and-advocacy/represent-your-profession</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H118" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I118" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J118" t="n">
         <v>10</v>
       </c>
       <c r="K118" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L118" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CAPE Program-Level Requirements</t>
+          <t>Continuing Professional Development</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -29161,37 +29937,37 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework/cape-program-level-requirements</t>
+          <t>https://www.racp.edu.au/fellows/continuing-professional-development</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="G119" t="n">
         <v>16</v>
       </c>
       <c r="H119" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I119" t="n">
+        <v>14</v>
+      </c>
+      <c r="J119" t="n">
+        <v>9</v>
+      </c>
+      <c r="K119" t="n">
+        <v>9</v>
+      </c>
+      <c r="L119" t="n">
         <v>16</v>
-      </c>
-      <c r="J119" t="n">
-        <v>6</v>
-      </c>
-      <c r="K119" t="n">
-        <v>5</v>
-      </c>
-      <c r="L119" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Prevocational Training and Entry to Basic Training</t>
+          <t>CPD Recognition and Assessment Framework</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -29211,37 +29987,37 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/become-a-physician/entry-into-basic-training/prevocational-training-and-entry-to-basic-training</t>
+          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H120" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I120" t="n">
         <v>15</v>
       </c>
       <c r="J120" t="n">
+        <v>10</v>
+      </c>
+      <c r="K120" t="n">
         <v>8</v>
       </c>
-      <c r="K120" t="n">
-        <v>11</v>
-      </c>
       <c r="L120" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Position design and posting</t>
+          <t>CAPE Program-Level Requirements</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -29261,7 +30037,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/local-selection/position-design-and-posting</t>
+          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework/cape-program-level-requirements</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -29270,28 +30046,28 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I121" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J121" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K121" t="n">
         <v>5</v>
       </c>
       <c r="L121" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Student Scholarships &amp; Prizes</t>
+          <t>Prevocational Training and Entry to Basic Training</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -29311,28 +30087,28 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/foundation/student-scholarships-and-prizes</t>
+          <t>https://www.racp.edu.au/become-a-physician/entry-into-basic-training/prevocational-training-and-entry-to-basic-training</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H122" t="n">
         <v>10</v>
       </c>
       <c r="I122" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J122" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K122" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L122" t="n">
         <v>14</v>
@@ -29341,7 +30117,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Selection into Training Quality Assurance and Improvement</t>
+          <t>Position design and posting</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -29361,37 +30137,37 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/become-a-physician/selection-into-training-quality-assurance-and-improvement</t>
+          <t>https://www.racp.edu.au/fellows/local-selection/position-design-and-posting</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H123" t="n">
+        <v>9</v>
+      </c>
+      <c r="I123" t="n">
+        <v>15</v>
+      </c>
+      <c r="J123" t="n">
         <v>8</v>
       </c>
-      <c r="I123" t="n">
-        <v>9</v>
-      </c>
-      <c r="J123" t="n">
-        <v>9</v>
-      </c>
       <c r="K123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L123" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Becoming a Fellow</t>
+          <t>Student Scholarships &amp; Prizes</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -29411,37 +30187,37 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/becoming-a-fellow</t>
+          <t>https://www.racp.edu.au/foundation/student-scholarships-and-prizes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="G124" t="n">
         <v>14</v>
       </c>
       <c r="H124" t="n">
+        <v>10</v>
+      </c>
+      <c r="I124" t="n">
+        <v>13</v>
+      </c>
+      <c r="J124" t="n">
+        <v>7</v>
+      </c>
+      <c r="K124" t="n">
         <v>8</v>
       </c>
-      <c r="I124" t="n">
+      <c r="L124" t="n">
         <v>14</v>
-      </c>
-      <c r="J124" t="n">
-        <v>6</v>
-      </c>
-      <c r="K124" t="n">
-        <v>3</v>
-      </c>
-      <c r="L124" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>International Grants</t>
+          <t>Selection into Training Quality Assurance and Improvement</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -29461,37 +30237,37 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/foundation/international-grants</t>
+          <t>https://www.racp.edu.au/become-a-physician/selection-into-training-quality-assurance-and-improvement</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H125" t="n">
+        <v>8</v>
+      </c>
+      <c r="I125" t="n">
         <v>9</v>
       </c>
-      <c r="I125" t="n">
-        <v>13</v>
-      </c>
       <c r="J125" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K125" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L125" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Our recipients</t>
+          <t>Becoming a Fellow</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -29511,7 +30287,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/foundation/our-recipients</t>
+          <t>https://www.racp.edu.au/fellows/becoming-a-fellow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -29520,28 +30296,28 @@
         </is>
       </c>
       <c r="G126" t="n">
+        <v>14</v>
+      </c>
+      <c r="H126" t="n">
+        <v>8</v>
+      </c>
+      <c r="I126" t="n">
+        <v>14</v>
+      </c>
+      <c r="J126" t="n">
+        <v>6</v>
+      </c>
+      <c r="K126" t="n">
+        <v>3</v>
+      </c>
+      <c r="L126" t="n">
         <v>13</v>
-      </c>
-      <c r="H126" t="n">
-        <v>6</v>
-      </c>
-      <c r="I126" t="n">
-        <v>13</v>
-      </c>
-      <c r="J126" t="n">
-        <v>7</v>
-      </c>
-      <c r="K126" t="n">
-        <v>6</v>
-      </c>
-      <c r="L126" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>News &amp; Events</t>
+          <t>International Grants</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -29561,37 +30337,37 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/news-and-events</t>
+          <t>https://www.racp.edu.au/foundation/international-grants</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H127" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I127" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J127" t="n">
         <v>6</v>
       </c>
       <c r="K127" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L127" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>New Fellow Survey</t>
+          <t>Our recipients</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -29611,7 +30387,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/becoming-a-fellow/new-fellow-survey</t>
+          <t>https://www.racp.edu.au/foundation/our-recipients</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -29620,21 +30396,121 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H128" t="n">
         <v>6</v>
       </c>
       <c r="I128" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J128" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K128" t="n">
         <v>6</v>
       </c>
       <c r="L128" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>News &amp; Events</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>RACP</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>RACP Member Hospital (AU)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://www.racp.edu.au/news-and-events</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Dr. Sarah Williams</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>12</v>
+      </c>
+      <c r="H129" t="n">
+        <v>5</v>
+      </c>
+      <c r="I129" t="n">
+        <v>11</v>
+      </c>
+      <c r="J129" t="n">
+        <v>6</v>
+      </c>
+      <c r="K129" t="n">
+        <v>6</v>
+      </c>
+      <c r="L129" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>New Fellow Survey</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>RACP</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>RACP Member Hospital (AU)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://www.racp.edu.au/fellows/becoming-a-fellow/new-fellow-survey</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Dr. James Chen</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>12</v>
+      </c>
+      <c r="H130" t="n">
+        <v>6</v>
+      </c>
+      <c r="I130" t="n">
+        <v>12</v>
+      </c>
+      <c r="J130" t="n">
+        <v>5</v>
+      </c>
+      <c r="K130" t="n">
+        <v>6</v>
+      </c>
+      <c r="L130" t="n">
         <v>12</v>
       </c>
     </row>
@@ -29649,7 +30525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29667,7 +30543,7 @@
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
   </cols>
@@ -29818,7 +30694,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -29898,7 +30774,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -29974,7 +30850,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -30050,7 +30926,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -30126,7 +31002,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -30206,7 +31082,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -30290,7 +31166,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -30374,7 +31250,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -30458,7 +31334,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -30538,7 +31414,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -30622,7 +31498,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -30702,7 +31578,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -30723,46 +31599,50 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Western_Health</t>
+          <t>WA_Health</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Team Leader - Child &amp; Adolescent Psychiatry Service</t>
+          <t>Fellow - Trauma Surgery</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Psychiatry</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Senior Registrar</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Western Health</t>
+          <t>WA Health</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://careers.wh.org.au/job/Team-Leader-Child-&amp;-Adolescent-Psychiatry-Service/1362919266/</t>
+          <t>https://medcareerswa.health.wa.gov.au/jobs/fellow-trauma-surgery-royal-perth-hospital-wa-australia-62611f69-14e4-407c-8c70-27588eb003f2</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>static_html</t>
+          <t>playwright</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -30772,7 +31652,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -30782,11 +31662,91 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>Yet to apply</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dr. Priya Sharma</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Western_Health</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Team Leader - Child &amp; Adolescent Psychiatry Service</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Psychiatry</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Western Health</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://careers.wh.org.au/job/Team-Leader-Child-&amp;-Adolescent-Psychiatry-Service/1362919266/</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>17</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Primary — configured method</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Low Match</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2 days old</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
         </is>
@@ -30968,7 +31928,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -31052,7 +32012,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -31132,7 +32092,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -31216,7 +32176,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -31300,7 +32260,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -31384,7 +32344,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -31468,7 +32428,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -31552,7 +32512,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -31636,7 +32596,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -31720,7 +32680,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -31804,7 +32764,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -31888,7 +32848,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -31972,7 +32932,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
@@ -32056,7 +33016,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
@@ -32140,7 +33100,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -32179,7 +33139,7 @@
     <col width="29" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
   </cols>
@@ -32326,7 +33286,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -32406,7 +33366,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -32490,7 +33450,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -32570,7 +33530,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -32650,7 +33610,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -32730,7 +33690,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
+          <t>1 day old</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -32810,7 +33770,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -32894,7 +33854,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -32974,7 +33934,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -33054,7 +34014,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
+          <t>1 day old</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -33138,7 +34098,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -33222,7 +34182,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -33306,7 +34266,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
@@ -33386,7 +34346,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
@@ -33466,7 +34426,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
+          <t>1 day old</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -33656,7 +34616,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -33736,7 +34696,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -33816,7 +34776,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -33896,7 +34856,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -33976,7 +34936,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -34056,7 +35016,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -34140,7 +35100,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -34224,7 +35184,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -34308,7 +35268,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -34392,7 +35352,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -34476,7 +35436,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -34560,7 +35520,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -34644,7 +35604,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
@@ -34728,7 +35688,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
@@ -34812,7 +35772,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -35002,7 +35962,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -35082,7 +36042,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -35166,7 +36126,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -35250,7 +36210,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -35334,7 +36294,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -35414,7 +36374,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -35494,7 +36454,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -35574,7 +36534,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -35787,7 +36747,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -35867,7 +36827,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -35952,7 +36912,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -35991,7 +36951,7 @@
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
   </cols>
@@ -36165,7 +37125,7 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -36240,7 +37200,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -36325,7 +37285,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -36410,7 +37370,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -36490,7 +37450,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -36570,7 +37530,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -36650,7 +37610,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -36730,7 +37690,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -36815,7 +37775,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -36900,7 +37860,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -36985,7 +37945,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -37065,7 +38025,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -37145,7 +38105,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -37230,7 +38190,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -37315,7 +38275,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -37395,7 +38355,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -37475,7 +38435,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -37555,7 +38515,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -37635,7 +38595,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -37715,7 +38675,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -37800,7 +38760,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -37880,7 +38840,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -37960,7 +38920,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -37975,7 +38935,6 @@
           <t>2027 Rheumatology Registrar  - Unaccredited</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -37996,7 +38955,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>01-07-2026</t>
@@ -38042,10 +39000,9 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
       <c r="S25" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -38082,7 +39039,7 @@
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
   </cols>
@@ -38260,7 +39217,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -38340,7 +39297,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -38425,7 +39382,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -38505,7 +39462,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -38585,7 +39542,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -38665,7 +39622,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -38745,7 +39702,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -38830,7 +39787,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -38910,7 +39867,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -38995,7 +39952,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -39080,7 +40037,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -39160,7 +40117,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -39240,7 +40197,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -39320,7 +40277,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -39400,7 +40357,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -39480,7 +40437,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -39495,7 +40452,6 @@
           <t>2026 Paediatric Emergency Registrar</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -39516,7 +40472,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>01-07-2026</t>
@@ -39562,10 +40517,9 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -39578,7 +40532,6 @@
           <t>2027 Unaccredited Geriatric Medicine Registrar</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -39599,7 +40552,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>01-07-2026</t>
@@ -39645,10 +40597,9 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
       <c r="S19" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -39666,7 +40617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -39685,7 +40636,7 @@
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
   </cols>
@@ -39858,7 +40809,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -39943,7 +40894,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -40028,7 +40979,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -40113,7 +41064,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -40198,7 +41149,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -40283,7 +41234,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -40368,7 +41319,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -40453,7 +41404,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -40538,7 +41489,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -40618,7 +41569,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -40698,7 +41649,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -40778,7 +41729,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -40863,7 +41814,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -40948,7 +41899,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -41028,7 +41979,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -41113,7 +42064,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -41198,7 +42149,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -41283,7 +42234,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -41368,7 +42319,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -41453,7 +42404,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -41533,7 +42484,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -41618,7 +42569,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -41703,7 +42654,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -41788,12 +42739,99 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fellow - Trauma Surgery</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Senior Registrar</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>WA Health</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>02-07-2026 09:22</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://medcareerswa.health.wa.gov.au/jobs/fellow-trauma-surgery-royal-perth-hospital-wa-australia-62611f69-14e4-407c-8c70-27588eb003f2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>WA_Health</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Dr. Priya Sharma</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>23</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Primary — configured method</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
         </is>
       </c>
     </row>
@@ -42265,7 +43303,7 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>

--- a/Job_Tracker.xlsx
+++ b/Job_Tracker.xlsx
@@ -1878,7 +1878,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>02-07-2026</t>
@@ -1927,7 +1926,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -1945,7 +1943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1964,7 +1962,7 @@
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
   </cols>
@@ -2957,6 +2955,89 @@
         </is>
       </c>
       <c r="S12" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Palliative Medicine - Internal Locum</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Eastern Health</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>02-07-2026 14:00</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://careers.easternhealth.org.au/job/Burwood-East-Palliative-Medicine-Internal-Locum-VIC-3151/1363692566/</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Eastern_Health</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Dr. Ananya Patel</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>21</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Primary — configured method</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
         </is>
@@ -6293,7 +6374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11089,6 +11170,534 @@
         <v>0</v>
       </c>
       <c r="G145" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>SmartJobs_QLD</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Jobs_NT</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Careers_VIC</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>3</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Monash_Health</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
+        <v>24</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Western_Health</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="n">
+        <v>18</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>WA_Health</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>25</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Peninsula_Health</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>The_Womens</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Grampians_Health</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>15</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Eastern_Health</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" t="n">
+        <v>12</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>8</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>RANZCOG</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>RACP</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" t="n">
+        <v>24</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>JobRadars</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>PageUp</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>all_methods_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>02-07-2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Mercy_Workday</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="inlineStr">
         <is>
           <t>all_methods_failed</t>
         </is>
@@ -13215,7 +13824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S130"/>
+  <dimension ref="A1:S131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -19043,7 +19652,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>02-07-2026</t>
@@ -19092,7 +19700,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>
@@ -20362,7 +20969,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>02-07-2026</t>
@@ -20411,7 +21017,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch</t>
@@ -21317,22 +21922,18 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2027 Senior Registrar General Medicine</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Internal Medicine</t>
-        </is>
-      </c>
+          <t>Palliative Medicine - Internal Locum</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Senior Registrar</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Royal Children's Hospital</t>
+          <t>Eastern Health</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -21345,33 +21946,34 @@
           <t>VIC</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>02-07-2026</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>30-06-2026 21:27</t>
+          <t>02-07-2026 14:00</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Senior-Registrar-General-Medicine/1362878366/</t>
+          <t>https://careers.easternhealth.org.au/job/Burwood-East-Palliative-Medicine-Internal-Locum-VIC-3151/1363692566/</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>RCH</t>
+          <t>Eastern_Health</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="M99" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -21385,29 +21987,35 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Weak title relevance; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>2 days old</t>
-        </is>
-      </c>
+          <t>Yet to apply</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Weak title relevance; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2027 Paediatric Registrars VPAT (Advanced and Continuing Trainees)</t>
+          <t>2027 Senior Registrar General Medicine</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Internal Medicine</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Senior Registrar</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -21437,7 +22045,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Paediatric-Registrars-VPAT-%28Advanced-and-Continuing-Trainees%29/1361643566/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Senior-Registrar-General-Medicine/1362878366/</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -21447,11 +22055,11 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -21465,7 +22073,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch</t>
+          <t>Weak title relevance; Experience level mismatch</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -21475,19 +22083,14 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch</t>
+          <t>Weak title relevance; Experience level mismatch</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2027 Immunopathology Registrar / Fellow</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Pathology</t>
+          <t>2027 Paediatric Registrars VPAT (Advanced and Continuing Trainees)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -21522,7 +22125,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Immunopathology-Registrar-Fellow/1363389666/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Paediatric-Registrars-VPAT-%28Advanced-and-Continuing-Trainees%29/1361643566/</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -21532,11 +22135,11 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Dr. Priya Sharma</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -21567,12 +22170,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2027 RCH NICU - VPAT Registrar</t>
+          <t>2027 Immunopathology Registrar / Fellow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ICU</t>
+          <t>Pathology</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -21607,7 +22210,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-RCH-NICU-VPAT-Registrar/1363270566/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Immunopathology-Registrar-Fellow/1363389666/</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -21617,11 +22220,11 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Priya Sharma</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -21652,7 +22255,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Microbiology Registrar 2027</t>
+          <t>2027 RCH NICU - VPAT Registrar</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ICU</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -21687,7 +22295,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Microbiology-Registrar-2027/1363255766/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-RCH-NICU-VPAT-Registrar/1363270566/</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -21732,7 +22340,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2027 Allergy &amp; Immunology Fellow / Registrar</t>
+          <t>Microbiology Registrar 2027</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -21767,7 +22375,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Allergy-&amp;-Immunology-Fellow-Registrar/1363326766/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Microbiology-Registrar-2027/1363255766/</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -21781,7 +22389,7 @@
         </is>
       </c>
       <c r="M104" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -21812,17 +22420,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Neurology Consultant</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Neurology</t>
+          <t>2027 Allergy &amp; Immunology Fellow / Registrar</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21852,7 +22455,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Neurology-Consultant/1362944566/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Allergy-&amp;-Immunology-Fellow-Registrar/1363326766/</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -21862,11 +22465,11 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Dr. Michael O'Brien</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="M105" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -21897,17 +22500,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2027 Unaccredited Ophthalmology Registrar</t>
+          <t>Neurology Consultant</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Registrar</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21927,17 +22530,17 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>01-07-2026 09:20</t>
+          <t>30-06-2026 21:27</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Unaccredited-Ophthalmology-Registrar/1357689666/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Neurology-Consultant/1362944566/</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -21947,11 +22550,11 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Michael O'Brien</t>
         </is>
       </c>
       <c r="M106" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -21970,7 +22573,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -21982,61 +22585,61 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Paediatrics &amp; Child Health</t>
+          <t>2027 Unaccredited Ophthalmology Registrar</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Internal Medicine</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Fellow</t>
+          <t>Registrar</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>RACP Member Hospital (AU)</t>
+          <t>Royal Children's Hospital</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>nt</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>01-07-2026</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>30-06-2026 21:27</t>
+          <t>01-07-2026 09:20</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/basic-training/paediatrics-child-health</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Unaccredited-Ophthalmology-Registrar/1357689666/</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>RACP</t>
+          <t>RCH</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="M107" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
@@ -22050,24 +22653,24 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Weak title relevance; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>1 day old</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>Weak title relevance; Experience level mismatch</t>
+          <t>Weak title relevance; Specialty mismatch</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Adult Internal Medicine</t>
+          <t>Paediatrics &amp; Child Health</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -22107,7 +22710,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/basic-training/adult-internal-medicine</t>
+          <t>https://www.racp.edu.au/trainees/basic-training/paediatrics-child-health</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -22121,7 +22724,7 @@
         </is>
       </c>
       <c r="M108" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -22152,7 +22755,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Adolescent and Young Adult Medicine</t>
+          <t>Adult Internal Medicine</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -22192,7 +22795,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/adolescent-and-young-adult-medicine</t>
+          <t>https://www.racp.edu.au/trainees/basic-training/adult-internal-medicine</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -22237,7 +22840,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Addiction Medicine</t>
+          <t>Adolescent and Young Adult Medicine</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -22277,7 +22880,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/addiction-medicine</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/adolescent-and-young-adult-medicine</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -22291,7 +22894,7 @@
         </is>
       </c>
       <c r="M110" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -22322,7 +22925,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>New curricula</t>
+          <t>Addiction Medicine</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -22362,7 +22965,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/new-curricula</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/addiction-medicine</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -22407,7 +23010,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Advanced Training - New Curricula</t>
+          <t>New curricula</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -22447,7 +23050,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/recognition-of-prior-learning/advanced-training-new-curricula</t>
+          <t>https://www.racp.edu.au/trainees/new-curricula</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -22461,7 +23064,7 @@
         </is>
       </c>
       <c r="M112" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -22492,7 +23095,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Advanced Training - New Curricula</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -22532,7 +23135,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/cardiology</t>
+          <t>https://www.racp.edu.au/trainees/recognition-of-prior-learning/advanced-training-new-curricula</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -22546,7 +23149,7 @@
         </is>
       </c>
       <c r="M113" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -22577,7 +23180,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Post-Fellowship training</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -22617,7 +23220,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/multi-specialty-training-options/post-fellowship-training</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/cardiology</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -22631,7 +23234,7 @@
         </is>
       </c>
       <c r="M114" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
@@ -22662,7 +23265,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Prizes, grants, scholarships and fellowships</t>
+          <t>Post-Fellowship training</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Internal Medicine</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -22697,7 +23305,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/become-a-physician/prizes-grants-scholarships-and-fellowships</t>
+          <t>https://www.racp.edu.au/trainees/multi-specialty-training-options/post-fellowship-training</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -22711,7 +23319,7 @@
         </is>
       </c>
       <c r="M115" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
@@ -22725,7 +23333,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+          <t>Weak title relevance; Experience level mismatch</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -22735,19 +23343,19 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+          <t>Weak title relevance; Experience level mismatch</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>The President's Message</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>ENT</t>
+          <t>Prizes, grants, scholarships and fellowships</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Fellow</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -22762,7 +23370,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -22777,7 +23385,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/news-and-events/presidents-message</t>
+          <t>https://www.racp.edu.au/become-a-physician/prizes-grants-scholarships-and-fellowships</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -22791,7 +23399,7 @@
         </is>
       </c>
       <c r="M116" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N116" t="inlineStr">
         <is>
@@ -22822,7 +23430,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Supervisor Professional Development Program</t>
+          <t>The President's Message</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -22830,11 +23438,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Fellow</t>
-        </is>
-      </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -22862,7 +23465,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/supervision/supervisor-professional-development-program</t>
+          <t>https://www.racp.edu.au/news-and-events/presidents-message</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -22872,7 +23475,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="M117" t="n">
@@ -22907,7 +23510,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Represent your Profession</t>
+          <t>Supervisor Professional Development Program</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -22915,6 +23518,11 @@
           <t>ENT</t>
         </is>
       </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Fellow</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -22942,7 +23550,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/policy-and-advocacy/represent-your-profession</t>
+          <t>https://www.racp.edu.au/fellows/supervision/supervisor-professional-development-program</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -22952,7 +23560,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="M118" t="n">
@@ -22987,7 +23595,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Continuing Professional Development</t>
+          <t>Represent your Profession</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -22995,11 +23603,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Fellow</t>
-        </is>
-      </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -23027,7 +23630,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/continuing-professional-development</t>
+          <t>https://www.racp.edu.au/policy-and-advocacy/represent-your-profession</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -23037,11 +23640,11 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="M119" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
@@ -23072,7 +23675,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CPD Recognition and Assessment Framework</t>
+          <t>Continuing Professional Development</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -23112,7 +23715,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework</t>
+          <t>https://www.racp.edu.au/fellows/continuing-professional-development</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -23157,7 +23760,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CAPE Program-Level Requirements</t>
+          <t>CPD Recognition and Assessment Framework</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -23197,7 +23800,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework/cape-program-level-requirements</t>
+          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -23207,7 +23810,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="M121" t="n">
@@ -23242,7 +23845,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Prevocational Training and Entry to Basic Training</t>
+          <t>CAPE Program-Level Requirements</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -23250,6 +23853,11 @@
           <t>ENT</t>
         </is>
       </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Fellow</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -23277,7 +23885,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/become-a-physician/entry-into-basic-training/prevocational-training-and-entry-to-basic-training</t>
+          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework/cape-program-level-requirements</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -23291,7 +23899,7 @@
         </is>
       </c>
       <c r="M122" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
@@ -23322,7 +23930,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Position design and posting</t>
+          <t>Prevocational Training and Entry to Basic Training</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -23330,11 +23938,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Fellow</t>
-        </is>
-      </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -23362,7 +23965,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/local-selection/position-design-and-posting</t>
+          <t>https://www.racp.edu.au/become-a-physician/entry-into-basic-training/prevocational-training-and-entry-to-basic-training</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -23407,7 +24010,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Student Scholarships &amp; Prizes</t>
+          <t>Position design and posting</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -23415,6 +24018,11 @@
           <t>ENT</t>
         </is>
       </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Fellow</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -23442,7 +24050,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/foundation/student-scholarships-and-prizes</t>
+          <t>https://www.racp.edu.au/fellows/local-selection/position-design-and-posting</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -23452,11 +24060,11 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="M124" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
@@ -23487,7 +24095,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Selection into Training Quality Assurance and Improvement</t>
+          <t>Student Scholarships &amp; Prizes</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -23522,7 +24130,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/become-a-physician/selection-into-training-quality-assurance-and-improvement</t>
+          <t>https://www.racp.edu.au/foundation/student-scholarships-and-prizes</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -23567,7 +24175,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Becoming a Fellow</t>
+          <t>Selection into Training Quality Assurance and Improvement</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -23575,11 +24183,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Fellow</t>
-        </is>
-      </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -23607,7 +24210,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/becoming-a-fellow</t>
+          <t>https://www.racp.edu.au/become-a-physician/selection-into-training-quality-assurance-and-improvement</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -23617,7 +24220,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -23652,12 +24255,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>International Grants</t>
+          <t>Becoming a Fellow</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ENT</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Fellow</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -23687,7 +24295,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/foundation/international-grants</t>
+          <t>https://www.racp.edu.au/fellows/becoming-a-fellow</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -23701,7 +24309,7 @@
         </is>
       </c>
       <c r="M127" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -23732,12 +24340,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Our recipients</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>ENT</t>
+          <t>International Grants</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -23767,7 +24375,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/foundation/our-recipients</t>
+          <t>https://www.racp.edu.au/foundation/international-grants</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -23812,7 +24420,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>News &amp; Events</t>
+          <t>Our recipients</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -23847,7 +24455,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/news-and-events</t>
+          <t>https://www.racp.edu.au/foundation/our-recipients</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -23857,11 +24465,11 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="M129" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
@@ -23892,7 +24500,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>New Fellow Survey</t>
+          <t>News &amp; Events</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -23900,11 +24508,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Fellow</t>
-        </is>
-      </c>
       <c r="D130" t="inlineStr">
         <is>
           <t>RACP Member Hospital (AU)</t>
@@ -23932,7 +24535,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/becoming-a-fellow/new-fellow-survey</t>
+          <t>https://www.racp.edu.au/news-and-events</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -23942,7 +24545,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="M130" t="n">
@@ -23969,6 +24572,91 @@
         </is>
       </c>
       <c r="S130" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>New Fellow Survey</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ENT</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Fellow</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>RACP Member Hospital (AU)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>nt</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>30-06-2026 21:27</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>https://www.racp.edu.au/fellows/becoming-a-fellow/new-fellow-survey</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>RACP</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Dr. James Chen</t>
+        </is>
+      </c>
+      <c r="M131" t="n">
+        <v>12</v>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Primary — configured method</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>2 days old</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Experience level mismatch</t>
         </is>
@@ -23985,7 +24673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:L131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -28917,17 +29605,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2027 Senior Registrar General Medicine</t>
+          <t>Palliative Medicine - Internal Locum</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RCH</t>
+          <t>Eastern_Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Royal Children's Hospital</t>
+          <t>Eastern Health</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -28937,37 +29625,37 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Senior-Registrar-General-Medicine/1362878366/</t>
+          <t>https://careers.easternhealth.org.au/job/Burwood-East-Palliative-Medicine-Internal-Locum-VIC-3151/1363692566/</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H99" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I99" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="J99" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="K99" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="L99" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2027 Paediatric Registrars VPAT (Advanced and Continuing Trainees)</t>
+          <t>2027 Senior Registrar General Medicine</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -28987,37 +29675,37 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Paediatric-Registrars-VPAT-%28Advanced-and-Continuing-Trainees%29/1361643566/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Senior-Registrar-General-Medicine/1362878366/</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H100" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I100" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="J100" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K100" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="L100" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2027 Immunopathology Registrar / Fellow</t>
+          <t>2027 Paediatric Registrars VPAT (Advanced and Continuing Trainees)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -29037,37 +29725,37 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Immunopathology-Registrar-Fellow/1363389666/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Paediatric-Registrars-VPAT-%28Advanced-and-Continuing-Trainees%29/1361643566/</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dr. Priya Sharma</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H101" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I101" t="n">
         <v>16</v>
       </c>
       <c r="J101" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K101" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L101" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2027 RCH NICU - VPAT Registrar</t>
+          <t>2027 Immunopathology Registrar / Fellow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -29087,37 +29775,37 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-RCH-NICU-VPAT-Registrar/1363270566/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Immunopathology-Registrar-Fellow/1363389666/</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Priya Sharma</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H102" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I102" t="n">
+        <v>16</v>
+      </c>
+      <c r="J102" t="n">
+        <v>35</v>
+      </c>
+      <c r="K102" t="n">
         <v>12</v>
       </c>
-      <c r="J102" t="n">
-        <v>34</v>
-      </c>
-      <c r="K102" t="n">
-        <v>13</v>
-      </c>
       <c r="L102" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Microbiology Registrar 2027</t>
+          <t>2027 RCH NICU - VPAT Registrar</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -29137,7 +29825,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Microbiology-Registrar-2027/1363255766/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-RCH-NICU-VPAT-Registrar/1363270566/</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -29149,10 +29837,10 @@
         <v>34</v>
       </c>
       <c r="H103" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I103" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J103" t="n">
         <v>34</v>
@@ -29161,13 +29849,13 @@
         <v>13</v>
       </c>
       <c r="L103" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2027 Allergy &amp; Immunology Fellow / Registrar</t>
+          <t>Microbiology Registrar 2027</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -29187,7 +29875,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Allergy-&amp;-Immunology-Fellow-Registrar/1363326766/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Microbiology-Registrar-2027/1363255766/</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -29196,28 +29884,28 @@
         </is>
       </c>
       <c r="G104" t="n">
+        <v>34</v>
+      </c>
+      <c r="H104" t="n">
         <v>33</v>
-      </c>
-      <c r="H104" t="n">
-        <v>32</v>
       </c>
       <c r="I104" t="n">
         <v>15</v>
       </c>
       <c r="J104" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K104" t="n">
+        <v>13</v>
+      </c>
+      <c r="L104" t="n">
         <v>14</v>
-      </c>
-      <c r="L104" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Neurology Consultant</t>
+          <t>2027 Allergy &amp; Immunology Fellow / Registrar</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -29237,28 +29925,28 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Neurology-Consultant/1362944566/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Allergy-&amp;-Immunology-Fellow-Registrar/1363326766/</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dr. Michael O'Brien</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H105" t="n">
+        <v>32</v>
+      </c>
+      <c r="I105" t="n">
         <v>15</v>
       </c>
-      <c r="I105" t="n">
+      <c r="J105" t="n">
+        <v>33</v>
+      </c>
+      <c r="K105" t="n">
         <v>14</v>
-      </c>
-      <c r="J105" t="n">
-        <v>14</v>
-      </c>
-      <c r="K105" t="n">
-        <v>31</v>
       </c>
       <c r="L105" t="n">
         <v>12</v>
@@ -29267,7 +29955,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2027 Unaccredited Ophthalmology Registrar</t>
+          <t>Neurology Consultant</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -29287,87 +29975,87 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Unaccredited-Ophthalmology-Registrar/1357689666/</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-Neurology-Consultant/1362944566/</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dr. Ananya Patel</t>
+          <t>Dr. Michael O'Brien</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H106" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="I106" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J106" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K106" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="L106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Paediatrics &amp; Child Health</t>
+          <t>2027 Unaccredited Ophthalmology Registrar</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RACP</t>
+          <t>RCH</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>RACP Member Hospital (AU)</t>
+          <t>Royal Children's Hospital</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/basic-training/paediatrics-child-health</t>
+          <t>https://careers.rch.org.au/job/50-Flemington-Rd-2027-Unaccredited-Ophthalmology-Registrar/1357689666/</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Ananya Patel</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H107" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I107" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="J107" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K107" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="L107" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Adult Internal Medicine</t>
+          <t>Paediatrics &amp; Child Health</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -29387,7 +30075,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/basic-training/adult-internal-medicine</t>
+          <t>https://www.racp.edu.au/trainees/basic-training/paediatrics-child-health</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -29396,19 +30084,19 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I108" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J108" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="K108" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L108" t="n">
         <v>36</v>
@@ -29417,7 +30105,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Adolescent and Young Adult Medicine</t>
+          <t>Adult Internal Medicine</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -29437,7 +30125,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/adolescent-and-young-adult-medicine</t>
+          <t>https://www.racp.edu.au/trainees/basic-training/adult-internal-medicine</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -29449,25 +30137,25 @@
         <v>42</v>
       </c>
       <c r="H109" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I109" t="n">
         <v>42</v>
       </c>
       <c r="J109" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K109" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L109" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Addiction Medicine</t>
+          <t>Adolescent and Young Adult Medicine</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -29487,7 +30175,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/addiction-medicine</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/adolescent-and-young-adult-medicine</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -29496,28 +30184,28 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H110" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I110" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J110" t="n">
         <v>11</v>
       </c>
       <c r="K110" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L110" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>New curricula</t>
+          <t>Addiction Medicine</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -29537,7 +30225,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/new-curricula</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/addiction-medicine</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -29549,25 +30237,25 @@
         <v>41</v>
       </c>
       <c r="H111" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I111" t="n">
         <v>41</v>
       </c>
       <c r="J111" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K111" t="n">
         <v>34</v>
       </c>
       <c r="L111" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Advanced Training - New Curricula</t>
+          <t>New curricula</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -29587,7 +30275,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/recognition-of-prior-learning/advanced-training-new-curricula</t>
+          <t>https://www.racp.edu.au/trainees/new-curricula</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -29596,19 +30284,19 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H112" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I112" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J112" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K112" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L112" t="n">
         <v>35</v>
@@ -29617,7 +30305,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Advanced Training - New Curricula</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -29637,7 +30325,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/advanced-training/cardiology</t>
+          <t>https://www.racp.edu.au/trainees/recognition-of-prior-learning/advanced-training-new-curricula</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -29646,28 +30334,28 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H113" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I113" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J113" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K113" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L113" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Post-Fellowship training</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -29687,7 +30375,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/trainees/multi-specialty-training-options/post-fellowship-training</t>
+          <t>https://www.racp.edu.au/trainees/advanced-training/cardiology</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -29696,28 +30384,28 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H114" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I114" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J114" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K114" t="n">
         <v>33</v>
       </c>
       <c r="L114" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Prizes, grants, scholarships and fellowships</t>
+          <t>Post-Fellowship training</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -29737,7 +30425,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/become-a-physician/prizes-grants-scholarships-and-fellowships</t>
+          <t>https://www.racp.edu.au/trainees/multi-specialty-training-options/post-fellowship-training</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -29746,28 +30434,28 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="H115" t="n">
         <v>8</v>
       </c>
       <c r="I115" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J115" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K115" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="L115" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>The President's Message</t>
+          <t>Prizes, grants, scholarships and fellowships</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -29782,12 +30470,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/news-and-events/presidents-message</t>
+          <t>https://www.racp.edu.au/become-a-physician/prizes-grants-scholarships-and-fellowships</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -29796,28 +30484,28 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H116" t="n">
+        <v>8</v>
+      </c>
+      <c r="I116" t="n">
+        <v>22</v>
+      </c>
+      <c r="J116" t="n">
         <v>9</v>
       </c>
-      <c r="I116" t="n">
-        <v>17</v>
-      </c>
-      <c r="J116" t="n">
-        <v>10</v>
-      </c>
       <c r="K116" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L116" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Supervisor Professional Development Program</t>
+          <t>The President's Message</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -29837,12 +30525,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/supervision/supervisor-professional-development-program</t>
+          <t>https://www.racp.edu.au/news-and-events/presidents-message</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -29852,22 +30540,22 @@
         <v>9</v>
       </c>
       <c r="I117" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J117" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K117" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L117" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Represent your Profession</t>
+          <t>Supervisor Professional Development Program</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -29887,37 +30575,37 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/policy-and-advocacy/represent-your-profession</t>
+          <t>https://www.racp.edu.au/fellows/supervision/supervisor-professional-development-program</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="G118" t="n">
         <v>17</v>
       </c>
       <c r="H118" t="n">
+        <v>9</v>
+      </c>
+      <c r="I118" t="n">
+        <v>16</v>
+      </c>
+      <c r="J118" t="n">
+        <v>9</v>
+      </c>
+      <c r="K118" t="n">
         <v>8</v>
       </c>
-      <c r="I118" t="n">
+      <c r="L118" t="n">
         <v>17</v>
-      </c>
-      <c r="J118" t="n">
-        <v>10</v>
-      </c>
-      <c r="K118" t="n">
-        <v>9</v>
-      </c>
-      <c r="L118" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Continuing Professional Development</t>
+          <t>Represent your Profession</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -29937,37 +30625,37 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/continuing-professional-development</t>
+          <t>https://www.racp.edu.au/policy-and-advocacy/represent-your-profession</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H119" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I119" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K119" t="n">
         <v>9</v>
       </c>
       <c r="L119" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CPD Recognition and Assessment Framework</t>
+          <t>Continuing Professional Development</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -29987,7 +30675,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework</t>
+          <t>https://www.racp.edu.au/fellows/continuing-professional-development</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -29999,16 +30687,16 @@
         <v>16</v>
       </c>
       <c r="H120" t="n">
+        <v>6</v>
+      </c>
+      <c r="I120" t="n">
+        <v>14</v>
+      </c>
+      <c r="J120" t="n">
         <v>9</v>
       </c>
-      <c r="I120" t="n">
-        <v>15</v>
-      </c>
-      <c r="J120" t="n">
-        <v>10</v>
-      </c>
       <c r="K120" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L120" t="n">
         <v>16</v>
@@ -30017,7 +30705,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CAPE Program-Level Requirements</t>
+          <t>CPD Recognition and Assessment Framework</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -30037,37 +30725,37 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework/cape-program-level-requirements</t>
+          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="G121" t="n">
         <v>16</v>
       </c>
       <c r="H121" t="n">
+        <v>9</v>
+      </c>
+      <c r="I121" t="n">
+        <v>15</v>
+      </c>
+      <c r="J121" t="n">
+        <v>10</v>
+      </c>
+      <c r="K121" t="n">
         <v>8</v>
       </c>
-      <c r="I121" t="n">
+      <c r="L121" t="n">
         <v>16</v>
-      </c>
-      <c r="J121" t="n">
-        <v>6</v>
-      </c>
-      <c r="K121" t="n">
-        <v>5</v>
-      </c>
-      <c r="L121" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Prevocational Training and Entry to Basic Training</t>
+          <t>CAPE Program-Level Requirements</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -30087,7 +30775,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/become-a-physician/entry-into-basic-training/prevocational-training-and-entry-to-basic-training</t>
+          <t>https://www.racp.edu.au/fellows/cpd-recognition-assessment-framework/cape-program-level-requirements</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -30096,28 +30784,28 @@
         </is>
       </c>
       <c r="G122" t="n">
+        <v>16</v>
+      </c>
+      <c r="H122" t="n">
+        <v>8</v>
+      </c>
+      <c r="I122" t="n">
+        <v>16</v>
+      </c>
+      <c r="J122" t="n">
+        <v>6</v>
+      </c>
+      <c r="K122" t="n">
+        <v>5</v>
+      </c>
+      <c r="L122" t="n">
         <v>15</v>
-      </c>
-      <c r="H122" t="n">
-        <v>10</v>
-      </c>
-      <c r="I122" t="n">
-        <v>15</v>
-      </c>
-      <c r="J122" t="n">
-        <v>8</v>
-      </c>
-      <c r="K122" t="n">
-        <v>11</v>
-      </c>
-      <c r="L122" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Position design and posting</t>
+          <t>Prevocational Training and Entry to Basic Training</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -30137,7 +30825,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/local-selection/position-design-and-posting</t>
+          <t>https://www.racp.edu.au/become-a-physician/entry-into-basic-training/prevocational-training-and-entry-to-basic-training</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -30149,7 +30837,7 @@
         <v>15</v>
       </c>
       <c r="H123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I123" t="n">
         <v>15</v>
@@ -30158,16 +30846,16 @@
         <v>8</v>
       </c>
       <c r="K123" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L123" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Student Scholarships &amp; Prizes</t>
+          <t>Position design and posting</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -30187,37 +30875,37 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/foundation/student-scholarships-and-prizes</t>
+          <t>https://www.racp.edu.au/fellows/local-selection/position-design-and-posting</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H124" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I124" t="n">
+        <v>15</v>
+      </c>
+      <c r="J124" t="n">
+        <v>8</v>
+      </c>
+      <c r="K124" t="n">
+        <v>5</v>
+      </c>
+      <c r="L124" t="n">
         <v>13</v>
-      </c>
-      <c r="J124" t="n">
-        <v>7</v>
-      </c>
-      <c r="K124" t="n">
-        <v>8</v>
-      </c>
-      <c r="L124" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Selection into Training Quality Assurance and Improvement</t>
+          <t>Student Scholarships &amp; Prizes</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -30237,7 +30925,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/become-a-physician/selection-into-training-quality-assurance-and-improvement</t>
+          <t>https://www.racp.edu.au/foundation/student-scholarships-and-prizes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -30249,16 +30937,16 @@
         <v>14</v>
       </c>
       <c r="H125" t="n">
+        <v>10</v>
+      </c>
+      <c r="I125" t="n">
+        <v>13</v>
+      </c>
+      <c r="J125" t="n">
+        <v>7</v>
+      </c>
+      <c r="K125" t="n">
         <v>8</v>
-      </c>
-      <c r="I125" t="n">
-        <v>9</v>
-      </c>
-      <c r="J125" t="n">
-        <v>9</v>
-      </c>
-      <c r="K125" t="n">
-        <v>10</v>
       </c>
       <c r="L125" t="n">
         <v>14</v>
@@ -30267,7 +30955,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Becoming a Fellow</t>
+          <t>Selection into Training Quality Assurance and Improvement</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -30287,12 +30975,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/becoming-a-fellow</t>
+          <t>https://www.racp.edu.au/become-a-physician/selection-into-training-quality-assurance-and-improvement</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -30302,22 +30990,22 @@
         <v>8</v>
       </c>
       <c r="I126" t="n">
+        <v>9</v>
+      </c>
+      <c r="J126" t="n">
+        <v>9</v>
+      </c>
+      <c r="K126" t="n">
+        <v>10</v>
+      </c>
+      <c r="L126" t="n">
         <v>14</v>
-      </c>
-      <c r="J126" t="n">
-        <v>6</v>
-      </c>
-      <c r="K126" t="n">
-        <v>3</v>
-      </c>
-      <c r="L126" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>International Grants</t>
+          <t>Becoming a Fellow</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -30337,7 +31025,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/foundation/international-grants</t>
+          <t>https://www.racp.edu.au/fellows/becoming-a-fellow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -30346,19 +31034,19 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H127" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I127" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J127" t="n">
         <v>6</v>
       </c>
       <c r="K127" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L127" t="n">
         <v>13</v>
@@ -30367,7 +31055,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Our recipients</t>
+          <t>International Grants</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -30387,7 +31075,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/foundation/our-recipients</t>
+          <t>https://www.racp.edu.au/foundation/international-grants</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -30399,25 +31087,25 @@
         <v>13</v>
       </c>
       <c r="H128" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I128" t="n">
         <v>13</v>
       </c>
       <c r="J128" t="n">
+        <v>6</v>
+      </c>
+      <c r="K128" t="n">
         <v>7</v>
       </c>
-      <c r="K128" t="n">
-        <v>6</v>
-      </c>
       <c r="L128" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>News &amp; Events</t>
+          <t>Our recipients</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -30437,25 +31125,25 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/news-and-events</t>
+          <t>https://www.racp.edu.au/foundation/our-recipients</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dr. Sarah Williams</t>
+          <t>Dr. James Chen</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I129" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J129" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K129" t="n">
         <v>6</v>
@@ -30467,7 +31155,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>New Fellow Survey</t>
+          <t>News &amp; Events</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -30487,30 +31175,80 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://www.racp.edu.au/fellows/becoming-a-fellow/new-fellow-survey</t>
+          <t>https://www.racp.edu.au/news-and-events</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dr. James Chen</t>
+          <t>Dr. Sarah Williams</t>
         </is>
       </c>
       <c r="G130" t="n">
         <v>12</v>
       </c>
       <c r="H130" t="n">
+        <v>5</v>
+      </c>
+      <c r="I130" t="n">
+        <v>11</v>
+      </c>
+      <c r="J130" t="n">
         <v>6</v>
-      </c>
-      <c r="I130" t="n">
-        <v>12</v>
-      </c>
-      <c r="J130" t="n">
-        <v>5</v>
       </c>
       <c r="K130" t="n">
         <v>6</v>
       </c>
       <c r="L130" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>New Fellow Survey</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>RACP</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>RACP Member Hospital (AU)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.racp.edu.au/fellows/becoming-a-fellow/new-fellow-survey</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Dr. James Chen</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>12</v>
+      </c>
+      <c r="H131" t="n">
+        <v>6</v>
+      </c>
+      <c r="I131" t="n">
+        <v>12</v>
+      </c>
+      <c r="J131" t="n">
+        <v>5</v>
+      </c>
+      <c r="K131" t="n">
+        <v>6</v>
+      </c>
+      <c r="L131" t="n">
         <v>12</v>
       </c>
     </row>
@@ -42779,7 +43517,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>02-07-2026</t>
@@ -42828,7 +43565,6 @@
           <t>Yet to apply</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>Weak title relevance; Specialty mismatch; Location mismatch</t>

--- a/Job_Tracker.xlsx
+++ b/Job_Tracker.xlsx
@@ -449,7 +449,7 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
@@ -595,7 +595,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -4256,10 +4255,9 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4267,7 +4265,6 @@
           <t>Paediatric Registrar in the role of a Research Fellow in Immunology and Allergy , Queensland Health</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -4288,7 +4285,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -4319,10 +4315,9 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4330,7 +4325,6 @@
           <t>Principal House Officer or Registrar or Senior Registrar - Beaudesert Hospital , Queensland Health</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>Senior Registrar</t>
@@ -4351,7 +4345,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -4382,10 +4375,9 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4393,7 +4385,6 @@
           <t>Senior Registrar or Registrar (Fellow in Cystic Fibrosis and Respiratory Infections) , Queensland Health</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>Senior Registrar</t>
@@ -4414,7 +4405,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -4445,10 +4435,9 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4481,7 +4470,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -4512,10 +4500,9 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4523,7 +4510,6 @@
           <t>Registrar (Advanced Trainee) CarePact , Queensland Health</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -4544,7 +4530,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -4575,10 +4560,9 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4586,7 +4570,6 @@
           <t>Registrar / Principal House Officer Emergency , Queensland Health</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>PHO</t>
@@ -4607,7 +4590,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -4638,10 +4620,9 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4649,7 +4630,6 @@
           <t>Principal House Officer / Registrar - Acute Surgical Unit , Queensland Health</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>PHO</t>
@@ -4670,7 +4650,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -4701,10 +4680,9 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4733,7 +4711,7 @@
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
@@ -4879,7 +4857,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4922,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -5009,7 +4987,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5047,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5112,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5177,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5237,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5302,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5367,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5427,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5487,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5552,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5612,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5677,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5742,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5752,6 @@
           <t>Registrar - Geriatric Advanced Trainee</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -5795,7 +5772,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -5826,10 +5802,9 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6004,7 +5979,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6044,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6104,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6169,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6234,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6294,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6359,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6419,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6479,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6539,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6599,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6659,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6836,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6896,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6961,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7026,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7086,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7146,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7211,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7276,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3 days old</t>
+          <t>4 days old</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7453,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7518,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7583,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7760,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7825,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7890,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7955,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8045,7 +8020,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8085,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8150,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8215,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8275,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8335,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8400,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8460,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8525,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8590,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8655,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8715,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8805,7 +8780,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8865,7 +8840,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8900,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -8990,7 +8965,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9025,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9085,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9145,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -9235,7 +9210,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9241,7 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
@@ -9407,7 +9382,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9442,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -9527,7 +9502,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -9587,7 +9562,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -9647,7 +9622,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -9712,7 +9687,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -9727,7 +9702,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>NSW Health</t>
@@ -9743,7 +9717,6 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -9774,10 +9747,9 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9810,7 +9782,6 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -9841,10 +9812,9 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9857,7 +9827,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>NSW Health</t>
@@ -9873,7 +9842,6 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -9904,10 +9872,9 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9936,7 +9903,7 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
@@ -10077,7 +10044,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10104,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10164,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -10257,7 +10224,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -10317,7 +10284,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10344,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -10437,7 +10404,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -10497,7 +10464,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10524,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10584,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -10682,7 +10649,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10709,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10769,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10829,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10894,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -10992,7 +10959,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -11052,7 +11019,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11034,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>NSW Health</t>
@@ -11083,7 +11049,6 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -11114,10 +11079,9 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11150,7 +11114,6 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -11181,10 +11144,9 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11197,7 +11159,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>NSW Health</t>
@@ -11213,7 +11174,6 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -11244,10 +11204,9 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11260,7 +11219,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>SA Health</t>
@@ -11276,7 +11234,6 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -11307,10 +11264,9 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11323,7 +11279,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>SA Health</t>
@@ -11339,7 +11294,6 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -11370,10 +11324,9 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11386,7 +11339,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>SA Health</t>
@@ -11402,7 +11354,6 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -11433,10 +11384,9 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11449,7 +11399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I225"/>
+  <dimension ref="A1:I241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19281,6 +19231,632 @@
         <v>16.4</v>
       </c>
       <c r="I225" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>SmartJobs_QLD</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>67</v>
+      </c>
+      <c r="H226" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>smartjobs_qld_failed: playwright=Page.goto: Timeout 90000ms exceeded.
+Call log:
+  - navigating to "https://smartjobs.qld.gov.au/jobto; static_html=HTTPSConnectionPool(host='smartjobs.qld.gov.au', port=443): Max retries exceeded with url: /jobtools</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Jobs_NT</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>37</v>
+      </c>
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
+        <v>39</v>
+      </c>
+      <c r="H227" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Careers_VIC</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>3</v>
+      </c>
+      <c r="H228" t="n">
+        <v>29</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>careers_vic_failed: playwright=zero_jobs_retry; playwright=0 jobs; static_html=403 Client Error: Forbidden for url: https://www.careers.vic.gov.au/jobs?keywords=registrar+medical</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Monash_Health</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>24</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>26</v>
+      </c>
+      <c r="H229" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Western_Health</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>15</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
+        <v>19</v>
+      </c>
+      <c r="H230" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>WA_Health</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>24</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
+        <v>30</v>
+      </c>
+      <c r="H231" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Peninsula_Health</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
+        <v>9</v>
+      </c>
+      <c r="H232" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>peninsula_health_failed: playwright=parser_found_nothing: page loaded but no job cards parsed; static_html=0 jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>The_Womens</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
+        <v>1</v>
+      </c>
+      <c r="H233" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>the_womens_failed: static_html=zero_jobs_retry; static_html=0 jobs; playwright=0 jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Grampians_Health</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>13</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
+        <v>16</v>
+      </c>
+      <c r="H234" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Eastern_Health</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>10</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
+        <v>12</v>
+      </c>
+      <c r="H235" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>RCH</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>7</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="n">
+        <v>8</v>
+      </c>
+      <c r="H236" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>RANZCOG</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="n">
+        <v>3</v>
+      </c>
+      <c r="H237" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>ranzcog_failed: playwright=blocked: RANZCOG jobs board blocked from github_actions — blocked: HTTP 403; all fallbacks empty; static_html=403 Client Error: Forbidden for url: https://jobs.ranzcog.edu.au/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>RACP</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>static_html</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>24</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
+        <v>24</v>
+      </c>
+      <c r="H238" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>JobRadars</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>5</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="n">
+        <v>9</v>
+      </c>
+      <c r="H239" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>PageUp</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>pageup_html</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>10</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="n">
+        <v>23</v>
+      </c>
+      <c r="H240" t="n">
+        <v>25</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Mercy_Workday</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>mercury_html</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>13</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="n">
+        <v>15</v>
+      </c>
+      <c r="H241" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I241" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -19312,7 +19888,7 @@
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
@@ -19451,7 +20027,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -19515,7 +20091,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -19579,7 +20155,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -19643,7 +20219,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -19707,7 +20283,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -19771,7 +20347,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -19835,7 +20411,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -19899,7 +20475,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -19963,7 +20539,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -20027,7 +20603,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -20091,7 +20667,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -20155,7 +20731,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -20219,7 +20795,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -20283,7 +20859,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -20347,7 +20923,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -20407,7 +20983,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -20471,7 +21047,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -20535,7 +21111,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -20599,7 +21175,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
+          <t>1 day old</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -20663,7 +21239,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -20761,7 +21337,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>05-07-2026</t>
         </is>
       </c>
     </row>
@@ -20798,7 +21374,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>05-07-2026</t>
         </is>
       </c>
     </row>
@@ -20835,7 +21411,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>05-07-2026</t>
         </is>
       </c>
     </row>
@@ -20872,7 +21448,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>05-07-2026</t>
         </is>
       </c>
     </row>
@@ -20909,7 +21485,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>05-07-2026</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21662,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -21151,7 +21727,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -21216,7 +21792,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -21281,7 +21857,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -21346,7 +21922,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -21406,7 +21982,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -21471,7 +22047,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -21536,7 +22112,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -21596,7 +22172,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -21661,7 +22237,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -21726,7 +22302,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -21791,7 +22367,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -21851,7 +22427,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -21911,7 +22487,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -21976,7 +22552,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22612,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22096,7 +22672,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22156,7 +22732,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22216,7 +22792,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22276,7 +22852,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22336,7 +22912,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22396,7 +22972,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22456,7 +23032,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22516,7 +23092,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22581,7 +23157,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22641,7 +23217,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22701,7 +23277,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22761,7 +23337,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22821,7 +23397,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22881,7 +23457,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -22941,7 +23517,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23001,7 +23577,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23061,7 +23637,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23121,7 +23697,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23181,7 +23757,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23241,7 +23817,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23301,7 +23877,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23361,7 +23937,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23421,7 +23997,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23452,7 +24028,7 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
@@ -23598,7 +24174,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23663,7 +24239,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23728,7 +24304,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23788,7 +24364,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23848,7 +24424,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23913,7 +24489,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -23978,7 +24554,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24614,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24098,7 +24674,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24158,7 +24734,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24218,7 +24794,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24283,7 +24859,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24348,7 +24924,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24413,7 +24989,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24473,7 +25049,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24538,7 +25114,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24603,7 +25179,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24663,7 +25239,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24723,7 +25299,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24788,7 +25364,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24853,7 +25429,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24913,7 +25489,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -24978,7 +25554,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25038,7 +25614,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25098,7 +25674,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25158,7 +25734,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25223,7 +25799,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25283,7 +25859,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25348,7 +25924,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25408,7 +25984,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25468,7 +26044,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25533,7 +26109,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25598,7 +26174,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25658,7 +26234,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25718,7 +26294,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25778,7 +26354,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25838,7 +26414,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25903,7 +26479,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -25968,7 +26544,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -26028,7 +26604,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -26093,7 +26669,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -26153,7 +26729,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -26218,7 +26794,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26859,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -26348,7 +26924,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -26408,7 +26984,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -26473,7 +27049,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -26533,7 +27109,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -26593,7 +27169,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -26653,7 +27229,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -26713,7 +27289,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -26773,7 +27349,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -26833,7 +27409,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -26893,7 +27469,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -26953,7 +27529,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -27013,7 +27589,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -27073,7 +27649,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -27133,7 +27709,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -27193,7 +27769,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -27228,7 +27804,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -27259,10 +27834,9 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -27270,7 +27844,6 @@
           <t>Paediatric Registrar in the role of a Research Fellow in Immunology and Allergy , Queensland Health</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -27291,7 +27864,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -27322,10 +27894,9 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -27333,7 +27904,6 @@
           <t>Principal House Officer or Registrar or Senior Registrar - Beaudesert Hospital , Queensland Health</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>Senior Registrar</t>
@@ -27354,7 +27924,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -27385,10 +27954,9 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -27396,7 +27964,6 @@
           <t>Senior Registrar or Registrar (Fellow in Cystic Fibrosis and Respiratory Infections) , Queensland Health</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>Senior Registrar</t>
@@ -27417,7 +27984,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -27448,10 +28014,9 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -27484,7 +28049,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -27515,10 +28079,9 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -27526,7 +28089,6 @@
           <t>Registrar (Advanced Trainee) CarePact , Queensland Health</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -27547,7 +28109,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -27578,10 +28139,9 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -27589,7 +28149,6 @@
           <t>Registrar / Principal House Officer Emergency , Queensland Health</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>PHO</t>
@@ -27610,7 +28169,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -27641,10 +28199,9 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -27652,7 +28209,6 @@
           <t>Principal House Officer / Registrar - Acute Surgical Unit , Queensland Health</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>PHO</t>
@@ -27673,7 +28229,6 @@
           <t>QLD</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -27704,10 +28259,9 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -27770,7 +28324,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -27835,7 +28389,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -27900,7 +28454,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -27965,7 +28519,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28030,7 +28584,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28090,7 +28644,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28155,7 +28709,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28220,7 +28774,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28280,7 +28834,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28345,7 +28899,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28410,7 +28964,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28475,7 +29029,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28535,7 +29089,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28595,7 +29149,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28660,7 +29214,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28720,7 +29274,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28780,7 +29334,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28840,7 +29394,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28900,7 +29454,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -28960,7 +29514,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29020,7 +29574,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29080,7 +29634,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29140,7 +29694,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29200,7 +29754,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29265,7 +29819,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29325,7 +29879,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29385,7 +29939,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29445,7 +29999,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29505,7 +30059,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29565,7 +30119,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29625,7 +30179,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29685,7 +30239,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29745,7 +30299,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29805,7 +30359,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29865,7 +30419,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29925,7 +30479,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -29985,7 +30539,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -30045,7 +30599,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -30105,7 +30659,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -30165,7 +30719,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -30225,7 +30779,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -30290,7 +30844,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -30355,7 +30909,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -30415,7 +30969,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -30480,7 +31034,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -30545,7 +31099,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -30605,7 +31159,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -30665,7 +31219,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -30725,7 +31279,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -30785,7 +31339,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -30850,7 +31404,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -30915,7 +31469,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -30980,7 +31534,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -31040,7 +31594,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -31100,7 +31654,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -31165,7 +31719,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -31230,7 +31784,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -31290,7 +31844,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -31350,7 +31904,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -31410,7 +31964,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -31470,7 +32024,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -31530,7 +32084,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -31595,7 +32149,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -31655,7 +32209,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -31715,7 +32269,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -31775,7 +32329,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>3 days old</t>
+          <t>4 days old</t>
         </is>
       </c>
     </row>
@@ -31835,7 +32389,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -31845,7 +32399,6 @@
           <t>Consultant Radiologist</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
           <t>Consultant</t>
@@ -31866,7 +32419,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -31897,10 +32449,9 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -31963,7 +32514,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32023,7 +32574,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32088,7 +32639,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32148,7 +32699,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32208,7 +32759,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32268,7 +32819,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32328,7 +32879,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32393,7 +32944,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32453,7 +33004,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32518,7 +33069,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32583,7 +33134,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32643,7 +33194,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32703,7 +33254,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32763,7 +33314,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32823,7 +33374,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32883,7 +33434,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -32943,7 +33494,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>3 days old</t>
+          <t>4 days old</t>
         </is>
       </c>
     </row>
@@ -33003,7 +33554,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>3 days old</t>
+          <t>4 days old</t>
         </is>
       </c>
     </row>
@@ -33018,7 +33569,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -33034,7 +33584,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -33065,10 +33614,9 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -33126,7 +33674,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -33191,7 +33739,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -33256,7 +33804,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -33321,7 +33869,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -33386,7 +33934,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -33451,7 +33999,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -33516,7 +34064,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -33581,7 +34129,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -33646,7 +34194,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -33706,7 +34254,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -33766,7 +34314,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -33826,7 +34374,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -33891,7 +34439,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -33956,7 +34504,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -34016,7 +34564,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -34081,7 +34629,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -34146,7 +34694,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -34211,7 +34759,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -34276,7 +34824,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -34341,7 +34889,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -34401,7 +34949,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -34466,7 +35014,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -34531,7 +35079,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -34596,7 +35144,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -34661,7 +35209,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -34726,7 +35274,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -34791,7 +35339,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -34856,7 +35404,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -34921,7 +35469,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -34981,7 +35529,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -35046,7 +35594,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35111,7 +35659,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35171,7 +35719,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35779,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35296,7 +35844,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35356,7 +35904,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35421,7 +35969,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35481,7 +36029,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35546,7 +36094,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35611,7 +36159,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35676,7 +36224,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35736,7 +36284,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35796,7 +36344,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35856,7 +36404,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35916,7 +36464,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -35981,7 +36529,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -36046,7 +36594,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -36111,7 +36659,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -36171,7 +36719,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -36236,7 +36784,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -36296,7 +36844,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -36361,7 +36909,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -36426,7 +36974,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -36486,7 +37034,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -36551,7 +37099,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -36616,7 +37164,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -36681,7 +37229,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -36746,7 +37294,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -36806,7 +37354,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -36871,7 +37419,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -36936,7 +37484,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -36996,7 +37544,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -37061,7 +37609,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -37126,7 +37674,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -37186,7 +37734,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -37246,7 +37794,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -37311,7 +37859,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -37371,7 +37919,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -37436,7 +37984,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -37501,7 +38049,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -37511,7 +38059,6 @@
           <t>Registrar - Geriatric Advanced Trainee</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
         <is>
           <t>Registrar</t>
@@ -37532,7 +38079,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -37563,10 +38109,9 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O226" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -37629,7 +38174,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -37694,7 +38239,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -37754,7 +38299,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -37819,7 +38364,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -37884,7 +38429,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -37944,7 +38489,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -38009,7 +38554,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -38069,7 +38614,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -38129,7 +38674,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -38189,7 +38734,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -38249,7 +38794,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -38309,7 +38854,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -38374,7 +38919,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -38434,7 +38979,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -38499,7 +39044,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -38564,7 +39109,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -38624,7 +39169,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -38684,7 +39229,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -38749,7 +39294,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -38814,7 +39359,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>3 days old</t>
+          <t>4 days old</t>
         </is>
       </c>
     </row>
@@ -38879,7 +39424,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -38944,7 +39489,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -39009,7 +39554,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -39074,7 +39619,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -39139,7 +39684,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -39204,7 +39749,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -39269,7 +39814,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -39334,7 +39879,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -39399,7 +39944,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -39464,7 +40009,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -39529,7 +40074,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -39589,7 +40134,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -39649,7 +40194,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -39714,7 +40259,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -39774,7 +40319,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -39839,7 +40384,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -39904,7 +40449,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -39969,7 +40514,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -40029,7 +40574,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -40094,7 +40639,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -40154,7 +40699,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -40214,7 +40759,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -40279,7 +40824,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -40339,7 +40884,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -40399,7 +40944,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -40459,7 +41004,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -40524,7 +41069,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -40584,7 +41129,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -40644,7 +41189,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -40704,7 +41249,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -40764,7 +41309,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -40824,7 +41369,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -40889,7 +41434,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -40904,7 +41449,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
           <t>NSW Health</t>
@@ -40920,7 +41464,6 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -40951,10 +41494,9 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O280" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -40987,7 +41529,6 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -41018,10 +41559,9 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O281" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -41034,7 +41574,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
           <t>NSW Health</t>
@@ -41050,7 +41589,6 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -41081,10 +41619,9 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O282" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -41142,7 +41679,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -41202,7 +41739,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -41262,7 +41799,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -41322,7 +41859,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -41382,7 +41919,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -41442,7 +41979,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -41502,7 +42039,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -41562,7 +42099,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -41622,7 +42159,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -41682,7 +42219,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -41747,7 +42284,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -41807,7 +42344,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -41867,7 +42404,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -41927,7 +42464,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -41992,7 +42529,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -42057,7 +42594,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -42117,7 +42654,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -42132,7 +42669,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
           <t>NSW Health</t>
@@ -42148,7 +42684,6 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -42179,10 +42714,9 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O300" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -42215,7 +42749,6 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -42246,10 +42779,9 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O301" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -42262,7 +42794,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
           <t>NSW Health</t>
@@ -42278,7 +42809,6 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -42309,10 +42839,9 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O302" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -42325,7 +42854,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
           <t>SA Health</t>
@@ -42341,7 +42869,6 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -42372,10 +42899,9 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O303" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -42388,7 +42914,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
           <t>SA Health</t>
@@ -42404,7 +42929,6 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -42435,10 +42959,9 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O304" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -42451,7 +42974,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
           <t>SA Health</t>
@@ -42467,7 +42989,6 @@
           <t>SA</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -42498,10 +43019,9 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O305" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -57961,7 +58481,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -58021,7 +58541,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -58086,7 +58606,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -58117,7 +58637,7 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -58263,7 +58783,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -58323,7 +58843,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -58388,7 +58908,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -58453,7 +58973,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -58513,7 +59033,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -58573,7 +59093,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -58633,7 +59153,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -58693,7 +59213,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -58758,7 +59278,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -58823,7 +59343,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -58888,7 +59408,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -58948,7 +59468,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -59008,7 +59528,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -59073,7 +59593,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -59138,7 +59658,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -59198,7 +59718,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -59258,7 +59778,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -59318,7 +59838,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -59378,7 +59898,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -59438,7 +59958,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -59503,7 +60023,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -59563,7 +60083,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -59623,7 +60143,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -59683,7 +60203,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>3 days old</t>
+          <t>4 days old</t>
         </is>
       </c>
     </row>
@@ -59743,7 +60263,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -59753,7 +60273,6 @@
           <t>Consultant Radiologist</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>Consultant</t>
@@ -59774,7 +60293,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -59805,10 +60323,9 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -59837,7 +60354,7 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="55" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -59983,7 +60500,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60043,7 +60560,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60108,7 +60625,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60168,7 +60685,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60228,7 +60745,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60288,7 +60805,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60348,7 +60865,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60413,7 +60930,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60473,7 +60990,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60538,7 +61055,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60603,7 +61120,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60663,7 +61180,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60723,7 +61240,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60783,7 +61300,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60843,7 +61360,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60903,7 +61420,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -60963,7 +61480,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3 days old</t>
+          <t>4 days old</t>
         </is>
       </c>
     </row>
@@ -61023,7 +61540,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>3 days old</t>
+          <t>4 days old</t>
         </is>
       </c>
     </row>
@@ -61038,7 +61555,6 @@
           <t>ENT</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>Western Health</t>
@@ -61054,7 +61570,6 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>04-07-2026</t>
@@ -61085,10 +61600,9 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Yet to apply</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>1 day old</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -61258,7 +61772,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -61323,7 +61837,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -61388,7 +61902,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -61453,7 +61967,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -61518,7 +62032,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -61583,7 +62097,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -61648,7 +62162,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -61713,7 +62227,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -61778,7 +62292,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -61838,7 +62352,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -61898,7 +62412,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -61958,7 +62472,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -62023,7 +62537,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -62088,7 +62602,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -62148,7 +62662,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -62213,7 +62727,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -62278,7 +62792,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -62343,7 +62857,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -62408,7 +62922,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -62473,7 +62987,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -62533,7 +63047,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -62598,7 +63112,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -62663,7 +63177,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -62728,7 +63242,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
@@ -62793,7 +63307,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -62858,7 +63372,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -62923,7 +63437,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -62988,7 +63502,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -63053,7 +63567,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -63113,7 +63627,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1 day old</t>
+          <t>2 days old</t>
         </is>
       </c>
     </row>
@@ -63290,7 +63804,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -63355,7 +63869,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -63415,7 +63929,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -63475,7 +63989,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -63540,7 +64054,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -63600,7 +64114,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -63665,7 +64179,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -63725,7 +64239,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -63790,7 +64304,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -63855,7 +64369,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -63920,7 +64434,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -63980,7 +64494,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -64040,7 +64554,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -64100,7 +64614,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -64160,7 +64674,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -64337,7 +64851,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -64402,7 +64916,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -64467,7 +64981,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -64527,7 +65041,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -64592,7 +65106,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -64652,7 +65166,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -64717,7 +65231,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -64782,7 +65296,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -64842,7 +65356,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2 days old</t>
+          <t>3 days old</t>
         </is>
       </c>
     </row>
@@ -65019,7 +65533,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4 days old</t>
+          <t>5 days old</t>
         </is>
       </c>
     </row>
